--- a/research/traditional_assets/database/data/ghana/ghana_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/ghana/ghana_oilfield_svcs_equip.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.176493998100249</v>
+        <v>0.1760865131049984</v>
       </c>
       <c r="C2">
-        <v>115.1459224299227</v>
+        <v>114.3351118746832</v>
       </c>
       <c r="D2">
-        <v>108.1759224299227</v>
+        <v>108.4901118746832</v>
       </c>
       <c r="E2">
-        <v>-12.5</v>
+        <v>-11.375</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.125</v>
       </c>
       <c r="G2">
         <v>6.97</v>
@@ -1451,28 +1451,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0565875</v>
       </c>
       <c r="N2">
-        <v>27.93877551020408</v>
+        <v>27.88218801020408</v>
       </c>
       <c r="O2">
-        <v>6.98469387755102</v>
+        <v>6.970547002551021</v>
       </c>
       <c r="P2">
-        <v>20.95408163265306</v>
+        <v>20.91164100765306</v>
       </c>
       <c r="Q2">
-        <v>24.95408163265306</v>
+        <v>24.91164100765306</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.176493998100249</v>
+        <v>0.1774841041464631</v>
       </c>
       <c r="T2">
-        <v>0.7993082229751833</v>
+        <v>0.8053635883007529</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>493.7269805205051</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1760865131049984</v>
+        <v>0.1756790281097478</v>
       </c>
       <c r="C3">
-        <v>114.3351118746832</v>
+        <v>113.5261317185011</v>
       </c>
       <c r="D3">
-        <v>108.4901118746832</v>
+        <v>108.8061317185011</v>
       </c>
       <c r="E3">
-        <v>-11.375</v>
+        <v>-10.25</v>
       </c>
       <c r="F3">
-        <v>1.125</v>
+        <v>2.25</v>
       </c>
       <c r="G3">
         <v>6.97</v>
@@ -1533,28 +1533,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M3">
-        <v>0.0565875</v>
+        <v>0.113175</v>
       </c>
       <c r="N3">
-        <v>27.88218801020408</v>
+        <v>27.82560051020408</v>
       </c>
       <c r="O3">
-        <v>6.970547002551021</v>
+        <v>6.956400127551021</v>
       </c>
       <c r="P3">
-        <v>20.91164100765306</v>
+        <v>20.86920038265306</v>
       </c>
       <c r="Q3">
-        <v>24.91164100765306</v>
+        <v>24.86920038265306</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1774841041464631</v>
+        <v>0.1784944164385182</v>
       </c>
       <c r="T3">
-        <v>0.8053635883007529</v>
+        <v>0.8115425325105178</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>493.7269805205051</v>
+        <v>246.8634902602525</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1756790281097478</v>
+        <v>0.1752715431144972</v>
       </c>
       <c r="C4">
-        <v>113.5261317185011</v>
+        <v>112.7189980033627</v>
       </c>
       <c r="D4">
-        <v>108.8061317185011</v>
+        <v>109.1239980033627</v>
       </c>
       <c r="E4">
-        <v>-10.25</v>
+        <v>-9.125</v>
       </c>
       <c r="F4">
-        <v>2.25</v>
+        <v>3.375</v>
       </c>
       <c r="G4">
         <v>6.97</v>
@@ -1615,28 +1615,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M4">
-        <v>0.113175</v>
+        <v>0.1697625</v>
       </c>
       <c r="N4">
-        <v>27.82560051020408</v>
+        <v>27.76901301020408</v>
       </c>
       <c r="O4">
-        <v>6.956400127551021</v>
+        <v>6.94225325255102</v>
       </c>
       <c r="P4">
-        <v>20.86920038265306</v>
+        <v>20.82675975765306</v>
       </c>
       <c r="Q4">
-        <v>24.86920038265306</v>
+        <v>24.82675975765306</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1784944164385182</v>
+        <v>0.1795255599118528</v>
       </c>
       <c r="T4">
-        <v>0.8115425325105178</v>
+        <v>0.8178488776318241</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>246.8634902602525</v>
+        <v>164.5756601735017</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1752715431144972</v>
+        <v>0.1748640581192466</v>
       </c>
       <c r="C5">
-        <v>112.7189980033627</v>
+        <v>111.9137269592633</v>
       </c>
       <c r="D5">
-        <v>109.1239980033627</v>
+        <v>109.4437269592633</v>
       </c>
       <c r="E5">
-        <v>-9.125</v>
+        <v>-8</v>
       </c>
       <c r="F5">
-        <v>3.375</v>
+        <v>4.5</v>
       </c>
       <c r="G5">
         <v>6.97</v>
@@ -1697,28 +1697,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M5">
-        <v>0.1697625</v>
+        <v>0.22635</v>
       </c>
       <c r="N5">
-        <v>27.76901301020408</v>
+        <v>27.71242551020408</v>
       </c>
       <c r="O5">
-        <v>6.94225325255102</v>
+        <v>6.92810637755102</v>
       </c>
       <c r="P5">
-        <v>20.82675975765306</v>
+        <v>20.78431913265306</v>
       </c>
       <c r="Q5">
-        <v>24.82675975765306</v>
+        <v>24.78431913265306</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1795255599118528</v>
+        <v>0.1805781855408818</v>
       </c>
       <c r="T5">
-        <v>0.8178488776318241</v>
+        <v>0.8242866049431579</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>164.5756601735017</v>
+        <v>123.4317451301263</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1748640581192466</v>
+        <v>0.1744565731239959</v>
       </c>
       <c r="C6">
-        <v>111.9137269592633</v>
+        <v>111.1103350069705</v>
       </c>
       <c r="D6">
-        <v>109.4437269592633</v>
+        <v>109.7653350069705</v>
       </c>
       <c r="E6">
-        <v>-8</v>
+        <v>-6.875</v>
       </c>
       <c r="F6">
-        <v>4.5</v>
+        <v>5.625</v>
       </c>
       <c r="G6">
         <v>6.97</v>
@@ -1779,28 +1779,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M6">
-        <v>0.22635</v>
+        <v>0.2829375</v>
       </c>
       <c r="N6">
-        <v>27.71242551020408</v>
+        <v>27.65583801020408</v>
       </c>
       <c r="O6">
-        <v>6.92810637755102</v>
+        <v>6.913959502551021</v>
       </c>
       <c r="P6">
-        <v>20.78431913265306</v>
+        <v>20.74187850765306</v>
       </c>
       <c r="Q6">
-        <v>24.78431913265306</v>
+        <v>24.74187850765306</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1805781855408818</v>
+        <v>0.1816529717094694</v>
       </c>
       <c r="T6">
-        <v>0.8242866049431579</v>
+        <v>0.8308598633557827</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>123.4317451301263</v>
+        <v>98.74539610410102</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1744565731239959</v>
+        <v>0.1740490881287453</v>
       </c>
       <c r="C7">
-        <v>111.1103350069705</v>
+        <v>110.3088387608347</v>
       </c>
       <c r="D7">
-        <v>109.7653350069705</v>
+        <v>110.0888387608347</v>
       </c>
       <c r="E7">
-        <v>-6.875</v>
+        <v>-5.749999999999999</v>
       </c>
       <c r="F7">
-        <v>5.625</v>
+        <v>6.750000000000001</v>
       </c>
       <c r="G7">
         <v>6.97</v>
@@ -1861,28 +1861,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M7">
-        <v>0.2829375</v>
+        <v>0.339525</v>
       </c>
       <c r="N7">
-        <v>27.65583801020408</v>
+        <v>27.59925051020408</v>
       </c>
       <c r="O7">
-        <v>6.913959502551021</v>
+        <v>6.899812627551021</v>
       </c>
       <c r="P7">
-        <v>20.74187850765306</v>
+        <v>20.69943788265306</v>
       </c>
       <c r="Q7">
-        <v>24.74187850765306</v>
+        <v>24.69943788265306</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1816529717094694</v>
+        <v>0.182750625668878</v>
       </c>
       <c r="T7">
-        <v>0.8308598633557827</v>
+        <v>0.8375729783303782</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>98.74539610410102</v>
+        <v>82.28783008675084</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1740490881287453</v>
+        <v>0.1736416031334947</v>
       </c>
       <c r="C8">
-        <v>110.3088387608347</v>
+        <v>109.509255031651</v>
       </c>
       <c r="D8">
-        <v>110.0888387608347</v>
+        <v>110.414255031651</v>
       </c>
       <c r="E8">
-        <v>-5.75</v>
+        <v>-4.625000000000001</v>
       </c>
       <c r="F8">
-        <v>6.75</v>
+        <v>7.874999999999999</v>
       </c>
       <c r="G8">
         <v>6.97</v>
@@ -1943,28 +1943,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M8">
-        <v>0.339525</v>
+        <v>0.3961124999999999</v>
       </c>
       <c r="N8">
-        <v>27.59925051020408</v>
+        <v>27.54266301020408</v>
       </c>
       <c r="O8">
-        <v>6.899812627551021</v>
+        <v>6.88566575255102</v>
       </c>
       <c r="P8">
-        <v>20.69943788265306</v>
+        <v>20.65699725765306</v>
       </c>
       <c r="Q8">
-        <v>24.69943788265306</v>
+        <v>24.65699725765306</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.182750625668878</v>
+        <v>0.1838718850897792</v>
       </c>
       <c r="T8">
-        <v>0.8375729783303782</v>
+        <v>0.8444304613689436</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>82.28783008675086</v>
+        <v>70.53242578864359</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1736416031334947</v>
+        <v>0.1732341181382441</v>
       </c>
       <c r="C9">
-        <v>109.509255031651</v>
+        <v>108.7116008295704</v>
       </c>
       <c r="D9">
-        <v>110.414255031651</v>
+        <v>110.7416008295704</v>
       </c>
       <c r="E9">
-        <v>-4.624999999999999</v>
+        <v>-3.5</v>
       </c>
       <c r="F9">
-        <v>7.875000000000001</v>
+        <v>9</v>
       </c>
       <c r="G9">
         <v>6.97</v>
@@ -2025,28 +2025,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M9">
-        <v>0.3961125</v>
+        <v>0.4527</v>
       </c>
       <c r="N9">
-        <v>27.54266301020408</v>
+        <v>27.48607551020408</v>
       </c>
       <c r="O9">
-        <v>6.88566575255102</v>
+        <v>6.87151887755102</v>
       </c>
       <c r="P9">
-        <v>20.65699725765306</v>
+        <v>20.61455663265306</v>
       </c>
       <c r="Q9">
-        <v>24.65699725765306</v>
+        <v>24.61455663265306</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1838718850897792</v>
+        <v>0.1850175197154827</v>
       </c>
       <c r="T9">
-        <v>0.8444304613689436</v>
+        <v>0.8514370201257389</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>70.53242578864358</v>
+        <v>61.71587256506314</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1732341181382441</v>
+        <v>0.1728266331429935</v>
       </c>
       <c r="C10">
-        <v>108.7116008295704</v>
+        <v>107.9158933670641</v>
       </c>
       <c r="D10">
-        <v>110.7416008295704</v>
+        <v>111.0708933670641</v>
       </c>
       <c r="E10">
-        <v>-3.5</v>
+        <v>-2.375</v>
       </c>
       <c r="F10">
-        <v>9</v>
+        <v>10.125</v>
       </c>
       <c r="G10">
         <v>6.97</v>
@@ -2107,28 +2107,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M10">
-        <v>0.4527</v>
+        <v>0.5092875</v>
       </c>
       <c r="N10">
-        <v>27.48607551020408</v>
+        <v>27.42948801020408</v>
       </c>
       <c r="O10">
-        <v>6.87151887755102</v>
+        <v>6.857372002551021</v>
       </c>
       <c r="P10">
-        <v>20.61455663265306</v>
+        <v>20.57211600765306</v>
       </c>
       <c r="Q10">
-        <v>24.61455663265306</v>
+        <v>24.57211600765306</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1850175197154827</v>
+        <v>0.1861883331241686</v>
       </c>
       <c r="T10">
-        <v>0.8514370201257389</v>
+        <v>0.8585975691848809</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>61.71587256506314</v>
+        <v>54.85855339116723</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1728266331429935</v>
+        <v>0.1724191481477428</v>
       </c>
       <c r="C11">
-        <v>107.9158933670641</v>
+        <v>107.1221500619409</v>
       </c>
       <c r="D11">
-        <v>111.0708933670641</v>
+        <v>111.4021500619409</v>
       </c>
       <c r="E11">
-        <v>-2.375</v>
+        <v>-1.250000000000002</v>
       </c>
       <c r="F11">
-        <v>10.125</v>
+        <v>11.25</v>
       </c>
       <c r="G11">
         <v>6.97</v>
@@ -2189,28 +2189,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M11">
-        <v>0.5092875</v>
+        <v>0.5658749999999999</v>
       </c>
       <c r="N11">
-        <v>27.42948801020408</v>
+        <v>27.37290051020408</v>
       </c>
       <c r="O11">
-        <v>6.857372002551021</v>
+        <v>6.843225127551021</v>
       </c>
       <c r="P11">
-        <v>20.57211600765306</v>
+        <v>20.52967538265306</v>
       </c>
       <c r="Q11">
-        <v>24.57211600765306</v>
+        <v>24.52967538265306</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1861883331241686</v>
+        <v>0.1873851646086031</v>
       </c>
       <c r="T11">
-        <v>0.8585975691848809</v>
+        <v>0.8659172415564486</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>54.85855339116723</v>
+        <v>49.37269805205052</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1724191481477428</v>
+        <v>0.1720116631524922</v>
       </c>
       <c r="C12">
-        <v>107.1221500619409</v>
+        <v>106.3303885404174</v>
       </c>
       <c r="D12">
-        <v>111.4021500619409</v>
+        <v>111.7353885404174</v>
       </c>
       <c r="E12">
-        <v>-1.25</v>
+        <v>-0.125</v>
       </c>
       <c r="F12">
-        <v>11.25</v>
+        <v>12.375</v>
       </c>
       <c r="G12">
         <v>6.97</v>
@@ -2271,28 +2271,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M12">
-        <v>0.565875</v>
+        <v>0.6224624999999999</v>
       </c>
       <c r="N12">
-        <v>27.37290051020408</v>
+        <v>27.31631301020408</v>
       </c>
       <c r="O12">
-        <v>6.843225127551021</v>
+        <v>6.82907825255102</v>
       </c>
       <c r="P12">
-        <v>20.52967538265306</v>
+        <v>20.48723475765306</v>
       </c>
       <c r="Q12">
-        <v>24.52967538265306</v>
+        <v>24.48723475765306</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1873851646086031</v>
+        <v>0.1886088911825755</v>
       </c>
       <c r="T12">
-        <v>0.8659172415564486</v>
+        <v>0.8734014009476021</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>49.37269805205051</v>
+        <v>44.88427095640956</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1720116631524922</v>
+        <v>0.1716041781572416</v>
       </c>
       <c r="C13">
-        <v>106.3303885404174</v>
+        <v>105.5406266402452</v>
       </c>
       <c r="D13">
-        <v>111.7353885404174</v>
+        <v>112.0706266402452</v>
       </c>
       <c r="E13">
-        <v>-0.125</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>12.375</v>
+        <v>13.5</v>
       </c>
       <c r="G13">
         <v>6.97</v>
@@ -2353,28 +2353,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M13">
-        <v>0.6224624999999999</v>
+        <v>0.6790499999999999</v>
       </c>
       <c r="N13">
-        <v>27.31631301020408</v>
+        <v>27.25972551020408</v>
       </c>
       <c r="O13">
-        <v>6.82907825255102</v>
+        <v>6.81493137755102</v>
       </c>
       <c r="P13">
-        <v>20.48723475765306</v>
+        <v>20.44479413265306</v>
       </c>
       <c r="Q13">
-        <v>24.48723475765306</v>
+        <v>24.44479413265306</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1886088911825755</v>
+        <v>0.1898604297241382</v>
       </c>
       <c r="T13">
-        <v>0.8734014009476021</v>
+        <v>0.8810556548703725</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>44.88427095640956</v>
+        <v>41.14391504337543</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1716041781572416</v>
+        <v>0.1711966931619909</v>
       </c>
       <c r="C14">
-        <v>105.5406266402452</v>
+        <v>104.7528824138937</v>
       </c>
       <c r="D14">
-        <v>112.0706266402452</v>
+        <v>112.4078824138937</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>2.125</v>
       </c>
       <c r="F14">
-        <v>13.5</v>
+        <v>14.625</v>
       </c>
       <c r="G14">
         <v>6.97</v>
@@ -2435,28 +2435,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M14">
-        <v>0.6790499999999999</v>
+        <v>0.7356374999999999</v>
       </c>
       <c r="N14">
-        <v>27.25972551020408</v>
+        <v>27.20313801020408</v>
       </c>
       <c r="O14">
-        <v>6.81493137755102</v>
+        <v>6.800784502551021</v>
       </c>
       <c r="P14">
-        <v>20.44479413265306</v>
+        <v>20.40235350765306</v>
       </c>
       <c r="Q14">
-        <v>24.44479413265306</v>
+        <v>24.40235350765306</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1898604297241382</v>
+        <v>0.1911407392666563</v>
       </c>
       <c r="T14">
-        <v>0.8810556548703725</v>
+        <v>0.8888858686534366</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>41.14391504337543</v>
+        <v>37.97899850157732</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1711966931619909</v>
+        <v>0.1707892081667403</v>
       </c>
       <c r="C15">
-        <v>104.7528824138937</v>
+        <v>103.96717413179</v>
       </c>
       <c r="D15">
-        <v>112.4078824138937</v>
+        <v>112.74717413179</v>
       </c>
       <c r="E15">
-        <v>2.125</v>
+        <v>3.250000000000002</v>
       </c>
       <c r="F15">
-        <v>14.625</v>
+        <v>15.75</v>
       </c>
       <c r="G15">
         <v>6.97</v>
@@ -2517,28 +2517,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M15">
-        <v>0.7356374999999999</v>
+        <v>0.7922250000000001</v>
       </c>
       <c r="N15">
-        <v>27.20313801020408</v>
+        <v>27.14655051020408</v>
       </c>
       <c r="O15">
-        <v>6.800784502551021</v>
+        <v>6.786637627551021</v>
       </c>
       <c r="P15">
-        <v>20.40235350765306</v>
+        <v>20.35991288265306</v>
       </c>
       <c r="Q15">
-        <v>24.40235350765306</v>
+        <v>24.35991288265306</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1911407392666563</v>
+        <v>0.1924508234496981</v>
       </c>
       <c r="T15">
-        <v>0.8888858686534366</v>
+        <v>0.8968981804314557</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>37.97899850157732</v>
+        <v>35.26621289432179</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1707892081667403</v>
+        <v>0.1703817231714897</v>
       </c>
       <c r="C16">
-        <v>103.96717413179</v>
+        <v>103.1835202856192</v>
       </c>
       <c r="D16">
-        <v>112.74717413179</v>
+        <v>113.0885202856192</v>
       </c>
       <c r="E16">
-        <v>3.250000000000002</v>
+        <v>4.375000000000004</v>
       </c>
       <c r="F16">
-        <v>15.75</v>
+        <v>16.875</v>
       </c>
       <c r="G16">
         <v>6.97</v>
@@ -2599,28 +2599,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M16">
-        <v>0.7922250000000001</v>
+        <v>0.8488125000000002</v>
       </c>
       <c r="N16">
-        <v>27.14655051020408</v>
+        <v>27.08996301020408</v>
       </c>
       <c r="O16">
-        <v>6.786637627551021</v>
+        <v>6.77249075255102</v>
       </c>
       <c r="P16">
-        <v>20.35991288265306</v>
+        <v>20.31747225765306</v>
       </c>
       <c r="Q16">
-        <v>24.35991288265306</v>
+        <v>24.31747225765306</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1924508234496981</v>
+        <v>0.1937917331429291</v>
       </c>
       <c r="T16">
-        <v>0.8968981804314557</v>
+        <v>0.905099017192487</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>35.26621289432179</v>
+        <v>32.91513203470033</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1703817231714897</v>
+        <v>0.1699742381762391</v>
       </c>
       <c r="C17">
-        <v>103.1835202856192</v>
+        <v>102.4019395916831</v>
       </c>
       <c r="D17">
-        <v>113.0885202856192</v>
+        <v>113.4319395916831</v>
       </c>
       <c r="E17">
-        <v>4.375</v>
+        <v>5.5</v>
       </c>
       <c r="F17">
-        <v>16.875</v>
+        <v>18</v>
       </c>
       <c r="G17">
         <v>6.97</v>
@@ -2681,28 +2681,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M17">
-        <v>0.8488125</v>
+        <v>0.9054</v>
       </c>
       <c r="N17">
-        <v>27.08996301020408</v>
+        <v>27.03337551020408</v>
       </c>
       <c r="O17">
-        <v>6.77249075255102</v>
+        <v>6.75834387755102</v>
       </c>
       <c r="P17">
-        <v>20.31747225765306</v>
+        <v>20.27503163265306</v>
       </c>
       <c r="Q17">
-        <v>24.31747225765306</v>
+        <v>24.27503163265306</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1937917331429291</v>
+        <v>0.1951645692574275</v>
       </c>
       <c r="T17">
-        <v>0.905099017192487</v>
+        <v>0.913495111971638</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>32.91513203470033</v>
+        <v>30.85793628253157</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1699742381762391</v>
+        <v>0.1695667531809885</v>
       </c>
       <c r="C18">
-        <v>102.4019395916831</v>
+        <v>101.6224509943215</v>
       </c>
       <c r="D18">
-        <v>113.4319395916831</v>
+        <v>113.7774509943215</v>
       </c>
       <c r="E18">
-        <v>5.5</v>
+        <v>6.625</v>
       </c>
       <c r="F18">
-        <v>18</v>
+        <v>19.125</v>
       </c>
       <c r="G18">
         <v>6.97</v>
@@ -2763,28 +2763,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M18">
-        <v>0.9054</v>
+        <v>0.9619875</v>
       </c>
       <c r="N18">
-        <v>27.03337551020408</v>
+        <v>26.97678801020408</v>
       </c>
       <c r="O18">
-        <v>6.75834387755102</v>
+        <v>6.744197002551021</v>
       </c>
       <c r="P18">
-        <v>20.27503163265306</v>
+        <v>20.23259100765306</v>
       </c>
       <c r="Q18">
-        <v>24.27503163265306</v>
+        <v>24.23259100765306</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1951645692574275</v>
+        <v>0.1965704857602271</v>
       </c>
       <c r="T18">
-        <v>0.913495111971638</v>
+        <v>0.9220935222876363</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>30.85793628253157</v>
+        <v>29.04276356002971</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1695667531809885</v>
+        <v>0.1691592681857378</v>
       </c>
       <c r="C19">
-        <v>101.6224509943215</v>
+        <v>100.8450736693959</v>
       </c>
       <c r="D19">
-        <v>113.7774509943215</v>
+        <v>114.1250736693959</v>
       </c>
       <c r="E19">
-        <v>6.625</v>
+        <v>7.750000000000004</v>
       </c>
       <c r="F19">
-        <v>19.125</v>
+        <v>20.25</v>
       </c>
       <c r="G19">
         <v>6.97</v>
@@ -2845,28 +2845,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M19">
-        <v>0.9619875</v>
+        <v>1.018575</v>
       </c>
       <c r="N19">
-        <v>26.97678801020408</v>
+        <v>26.92020051020408</v>
       </c>
       <c r="O19">
-        <v>6.744197002551021</v>
+        <v>6.730050127551021</v>
       </c>
       <c r="P19">
-        <v>20.23259100765306</v>
+        <v>20.19015038265306</v>
       </c>
       <c r="Q19">
-        <v>24.23259100765306</v>
+        <v>24.19015038265306</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1965704857602271</v>
+        <v>0.1980106929094364</v>
       </c>
       <c r="T19">
-        <v>0.9220935222876363</v>
+        <v>0.9309016499284147</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>29.04276356002971</v>
+        <v>27.42927669558361</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1691592681857379</v>
+        <v>0.1687517831904873</v>
       </c>
       <c r="C20">
-        <v>100.8450736693958</v>
+        <v>100.0698270278365</v>
       </c>
       <c r="D20">
-        <v>114.1250736693958</v>
+        <v>114.4748270278365</v>
       </c>
       <c r="E20">
-        <v>7.75</v>
+        <v>8.875</v>
       </c>
       <c r="F20">
-        <v>20.25</v>
+        <v>21.375</v>
       </c>
       <c r="G20">
         <v>6.97</v>
@@ -2927,28 +2927,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M20">
-        <v>1.018575</v>
+        <v>1.0751625</v>
       </c>
       <c r="N20">
-        <v>26.92020051020408</v>
+        <v>26.86361301020408</v>
       </c>
       <c r="O20">
-        <v>6.730050127551021</v>
+        <v>6.71590325255102</v>
       </c>
       <c r="P20">
-        <v>20.19015038265306</v>
+        <v>20.14770975765306</v>
       </c>
       <c r="Q20">
-        <v>24.19015038265306</v>
+        <v>24.14770975765306</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1980106929094364</v>
+        <v>0.1994864607289966</v>
       </c>
       <c r="T20">
-        <v>0.9309016499284147</v>
+        <v>0.9399272622022991</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>27.42927669558362</v>
+        <v>25.98563055371079</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1687517831904873</v>
+        <v>0.1683442981952366</v>
       </c>
       <c r="C21">
-        <v>100.0698270278365</v>
+        <v>99.29673071925642</v>
       </c>
       <c r="D21">
-        <v>114.4748270278365</v>
+        <v>114.8267307192564</v>
       </c>
       <c r="E21">
-        <v>8.875</v>
+        <v>10</v>
       </c>
       <c r="F21">
-        <v>21.375</v>
+        <v>22.5</v>
       </c>
       <c r="G21">
         <v>6.97</v>
@@ -3009,28 +3009,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M21">
-        <v>1.0751625</v>
+        <v>1.13175</v>
       </c>
       <c r="N21">
-        <v>26.86361301020408</v>
+        <v>26.80702551020408</v>
       </c>
       <c r="O21">
-        <v>6.71590325255102</v>
+        <v>6.70175637755102</v>
       </c>
       <c r="P21">
-        <v>20.14770975765306</v>
+        <v>20.10526913265306</v>
       </c>
       <c r="Q21">
-        <v>24.14770975765306</v>
+        <v>24.10526913265306</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1994864607289966</v>
+        <v>0.2009991227440457</v>
       </c>
       <c r="T21">
-        <v>0.9399272622022991</v>
+        <v>0.9491785147830302</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>25.98563055371079</v>
+        <v>24.68634902602525</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1683442981952366</v>
+        <v>0.167936813199986</v>
       </c>
       <c r="C22">
-        <v>99.29673071925642</v>
+        <v>98.52580463563048</v>
       </c>
       <c r="D22">
-        <v>114.8267307192564</v>
+        <v>115.1808046356305</v>
       </c>
       <c r="E22">
-        <v>10</v>
+        <v>11.125</v>
       </c>
       <c r="F22">
-        <v>22.5</v>
+        <v>23.625</v>
       </c>
       <c r="G22">
         <v>6.97</v>
@@ -3091,28 +3091,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M22">
-        <v>1.13175</v>
+        <v>1.1883375</v>
       </c>
       <c r="N22">
-        <v>26.80702551020408</v>
+        <v>26.75043801020408</v>
       </c>
       <c r="O22">
-        <v>6.70175637755102</v>
+        <v>6.68760950255102</v>
       </c>
       <c r="P22">
-        <v>20.10526913265306</v>
+        <v>20.06282850765306</v>
       </c>
       <c r="Q22">
-        <v>24.10526913265306</v>
+        <v>24.06282850765306</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2009991227440457</v>
+        <v>0.2025500799999822</v>
       </c>
       <c r="T22">
-        <v>0.9491785147830302</v>
+        <v>0.9586639762898559</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>24.68634902602525</v>
+        <v>23.51080859621453</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.167936813199986</v>
+        <v>0.1675293282047353</v>
       </c>
       <c r="C23">
-        <v>98.52580463563048</v>
+        <v>97.75706891504423</v>
       </c>
       <c r="D23">
-        <v>115.1808046356305</v>
+        <v>115.5370689150442</v>
       </c>
       <c r="E23">
-        <v>11.125</v>
+        <v>12.25</v>
       </c>
       <c r="F23">
-        <v>23.625</v>
+        <v>24.75</v>
       </c>
       <c r="G23">
         <v>6.97</v>
@@ -3173,28 +3173,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M23">
-        <v>1.1883375</v>
+        <v>1.244925</v>
       </c>
       <c r="N23">
-        <v>26.75043801020408</v>
+        <v>26.69385051020408</v>
       </c>
       <c r="O23">
-        <v>6.68760950255102</v>
+        <v>6.673462627551021</v>
       </c>
       <c r="P23">
-        <v>20.06282850765306</v>
+        <v>20.02038788265306</v>
       </c>
       <c r="Q23">
-        <v>24.06282850765306</v>
+        <v>24.02038788265306</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2025500799999822</v>
+        <v>0.2041408053906863</v>
       </c>
       <c r="T23">
-        <v>0.9586639762898559</v>
+        <v>0.9683926547583951</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>23.51080859621453</v>
+        <v>22.44213547820478</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1675293282047353</v>
+        <v>0.1671218432094848</v>
       </c>
       <c r="C24">
-        <v>97.75706891504423</v>
+        <v>96.99054394551152</v>
       </c>
       <c r="D24">
-        <v>115.5370689150442</v>
+        <v>115.8955439455115</v>
       </c>
       <c r="E24">
-        <v>12.25</v>
+        <v>13.375</v>
       </c>
       <c r="F24">
-        <v>24.75</v>
+        <v>25.875</v>
       </c>
       <c r="G24">
         <v>6.97</v>
@@ -3255,28 +3255,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M24">
-        <v>1.244925</v>
+        <v>1.3015125</v>
       </c>
       <c r="N24">
-        <v>26.69385051020408</v>
+        <v>26.63726301020408</v>
       </c>
       <c r="O24">
-        <v>6.673462627551021</v>
+        <v>6.65931575255102</v>
       </c>
       <c r="P24">
-        <v>20.02038788265306</v>
+        <v>19.97794725765306</v>
       </c>
       <c r="Q24">
-        <v>24.02038788265306</v>
+        <v>23.97794725765306</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2041408053906863</v>
+        <v>0.2057728483240062</v>
       </c>
       <c r="T24">
-        <v>0.9683926547583951</v>
+        <v>0.9783740261741692</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>22.44213547820478</v>
+        <v>21.46639045741327</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1671218432094848</v>
+        <v>0.1667143582142341</v>
       </c>
       <c r="C25">
-        <v>96.99054394551152</v>
+        <v>96.22625036886416</v>
       </c>
       <c r="D25">
-        <v>115.8955439455115</v>
+        <v>116.2562503688642</v>
       </c>
       <c r="E25">
-        <v>13.375</v>
+        <v>14.5</v>
       </c>
       <c r="F25">
-        <v>25.875</v>
+        <v>27</v>
       </c>
       <c r="G25">
         <v>6.97</v>
@@ -3337,28 +3337,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M25">
-        <v>1.3015125</v>
+        <v>1.3581</v>
       </c>
       <c r="N25">
-        <v>26.63726301020408</v>
+        <v>26.58067551020408</v>
       </c>
       <c r="O25">
-        <v>6.65931575255102</v>
+        <v>6.64516887755102</v>
       </c>
       <c r="P25">
-        <v>19.97794725765306</v>
+        <v>19.93550663265306</v>
       </c>
       <c r="Q25">
-        <v>23.97794725765306</v>
+        <v>23.93550663265306</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2057728483240062</v>
+        <v>0.2074478397555712</v>
       </c>
       <c r="T25">
-        <v>0.9783740261741692</v>
+        <v>0.9886180652587795</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>21.46639045741327</v>
+        <v>20.57195752168771</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1667143582142341</v>
+        <v>0.1663068732189835</v>
       </c>
       <c r="C26">
-        <v>96.22625036886416</v>
+        <v>95.46420908471387</v>
       </c>
       <c r="D26">
-        <v>116.2562503688642</v>
+        <v>116.6192090847139</v>
       </c>
       <c r="E26">
-        <v>14.5</v>
+        <v>15.625</v>
       </c>
       <c r="F26">
-        <v>27</v>
+        <v>28.125</v>
       </c>
       <c r="G26">
         <v>6.97</v>
@@ -3419,28 +3419,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M26">
-        <v>1.3581</v>
+        <v>1.4146875</v>
       </c>
       <c r="N26">
-        <v>26.58067551020408</v>
+        <v>26.52408801020408</v>
       </c>
       <c r="O26">
-        <v>6.64516887755102</v>
+        <v>6.63102200255102</v>
       </c>
       <c r="P26">
-        <v>19.93550663265306</v>
+        <v>19.89306600765306</v>
       </c>
       <c r="Q26">
-        <v>23.93550663265306</v>
+        <v>23.89306600765306</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2074478397555712</v>
+        <v>0.2091674976253113</v>
       </c>
       <c r="T26">
-        <v>0.9886180652587795</v>
+        <v>0.9991352787189791</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>20.57195752168771</v>
+        <v>19.74907922082021</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1663068732189835</v>
+        <v>0.1658993882237329</v>
       </c>
       <c r="C27">
-        <v>95.46420908471387</v>
+        <v>94.70444125448884</v>
       </c>
       <c r="D27">
-        <v>116.6192090847139</v>
+        <v>116.9844412544888</v>
       </c>
       <c r="E27">
-        <v>15.625</v>
+        <v>16.75</v>
       </c>
       <c r="F27">
-        <v>28.125</v>
+        <v>29.25</v>
       </c>
       <c r="G27">
         <v>6.97</v>
@@ -3501,28 +3501,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M27">
-        <v>1.4146875</v>
+        <v>1.471275</v>
       </c>
       <c r="N27">
-        <v>26.52408801020408</v>
+        <v>26.46750051020408</v>
       </c>
       <c r="O27">
-        <v>6.63102200255102</v>
+        <v>6.616875127551021</v>
       </c>
       <c r="P27">
-        <v>19.89306600765306</v>
+        <v>19.85062538265306</v>
       </c>
       <c r="Q27">
-        <v>23.89306600765306</v>
+        <v>23.85062538265306</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2091674976253113</v>
+        <v>0.2109336327347742</v>
       </c>
       <c r="T27">
-        <v>0.9991352787189791</v>
+        <v>1.009936741191617</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>19.74907922082021</v>
+        <v>18.98949925078866</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1658993882237329</v>
+        <v>0.1654919032284823</v>
       </c>
       <c r="C28">
-        <v>94.70444125448884</v>
+        <v>93.94696830554662</v>
       </c>
       <c r="D28">
-        <v>116.9844412544888</v>
+        <v>117.3519683055466</v>
       </c>
       <c r="E28">
-        <v>16.75</v>
+        <v>17.875</v>
       </c>
       <c r="F28">
-        <v>29.25</v>
+        <v>30.375</v>
       </c>
       <c r="G28">
         <v>6.97</v>
@@ -3583,28 +3583,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M28">
-        <v>1.471275</v>
+        <v>1.5278625</v>
       </c>
       <c r="N28">
-        <v>26.46750051020408</v>
+        <v>26.41091301020408</v>
       </c>
       <c r="O28">
-        <v>6.616875127551021</v>
+        <v>6.60272825255102</v>
       </c>
       <c r="P28">
-        <v>19.85062538265306</v>
+        <v>19.80818475765306</v>
       </c>
       <c r="Q28">
-        <v>23.85062538265306</v>
+        <v>23.80818475765306</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2109336327347742</v>
+        <v>0.2127481551075099</v>
       </c>
       <c r="T28">
-        <v>1.009936741191617</v>
+        <v>1.021034134142957</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>18.98949925078866</v>
+        <v>18.28618446372241</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1654919032284823</v>
+        <v>0.1650844182332316</v>
       </c>
       <c r="C29">
-        <v>93.94696830554662</v>
+        <v>93.19181193536461</v>
       </c>
       <c r="D29">
-        <v>117.3519683055466</v>
+        <v>117.7218119353646</v>
       </c>
       <c r="E29">
-        <v>17.875</v>
+        <v>19</v>
       </c>
       <c r="F29">
-        <v>30.375</v>
+        <v>31.5</v>
       </c>
       <c r="G29">
         <v>6.97</v>
@@ -3665,28 +3665,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M29">
-        <v>1.5278625</v>
+        <v>1.58445</v>
       </c>
       <c r="N29">
-        <v>26.41091301020408</v>
+        <v>26.35432551020408</v>
       </c>
       <c r="O29">
-        <v>6.60272825255102</v>
+        <v>6.58858137755102</v>
       </c>
       <c r="P29">
-        <v>19.80818475765306</v>
+        <v>19.76574413265306</v>
       </c>
       <c r="Q29">
-        <v>23.80818475765306</v>
+        <v>23.76574413265306</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2127481551075099</v>
+        <v>0.2146130808794884</v>
       </c>
       <c r="T29">
-        <v>1.021034134142957</v>
+        <v>1.032439788009612</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>18.28618446372241</v>
+        <v>17.63310644716089</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1650844182332316</v>
+        <v>0.164676933237981</v>
       </c>
       <c r="C30">
-        <v>93.19181193536461</v>
+        <v>92.43899411580978</v>
       </c>
       <c r="D30">
-        <v>117.7218119353646</v>
+        <v>118.0939941158098</v>
       </c>
       <c r="E30">
-        <v>19</v>
+        <v>20.12500000000001</v>
       </c>
       <c r="F30">
-        <v>31.5</v>
+        <v>32.62500000000001</v>
       </c>
       <c r="G30">
         <v>6.97</v>
@@ -3747,28 +3747,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M30">
-        <v>1.58445</v>
+        <v>1.6410375</v>
       </c>
       <c r="N30">
-        <v>26.35432551020408</v>
+        <v>26.29773801020408</v>
       </c>
       <c r="O30">
-        <v>6.58858137755102</v>
+        <v>6.57443450255102</v>
       </c>
       <c r="P30">
-        <v>19.76574413265306</v>
+        <v>19.72330350765306</v>
       </c>
       <c r="Q30">
-        <v>23.76574413265306</v>
+        <v>23.72330350765306</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2146130808794884</v>
+        <v>0.2165305397718042</v>
       </c>
       <c r="T30">
-        <v>1.032439788009612</v>
+        <v>1.04416672790068</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>17.63310644716089</v>
+        <v>17.02506829381052</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.164676933237981</v>
+        <v>0.1642694482427303</v>
       </c>
       <c r="C31">
-        <v>92.43899411580979</v>
+        <v>91.68853709749023</v>
       </c>
       <c r="D31">
-        <v>118.0939941158098</v>
+        <v>118.4685370974902</v>
       </c>
       <c r="E31">
-        <v>20.125</v>
+        <v>21.25</v>
       </c>
       <c r="F31">
-        <v>32.625</v>
+        <v>33.75</v>
       </c>
       <c r="G31">
         <v>6.97</v>
@@ -3829,28 +3829,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M31">
-        <v>1.6410375</v>
+        <v>1.697625</v>
       </c>
       <c r="N31">
-        <v>26.29773801020408</v>
+        <v>26.24115051020408</v>
       </c>
       <c r="O31">
-        <v>6.57443450255102</v>
+        <v>6.560287627551021</v>
       </c>
       <c r="P31">
-        <v>19.72330350765306</v>
+        <v>19.68086288265306</v>
       </c>
       <c r="Q31">
-        <v>23.72330350765306</v>
+        <v>23.68086288265306</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2165305397718042</v>
+        <v>0.2185027832039005</v>
       </c>
       <c r="T31">
-        <v>1.04416672790068</v>
+        <v>1.056228723217207</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>17.02506829381052</v>
+        <v>16.45756601735017</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1642694482427303</v>
+        <v>0.1638619632474797</v>
       </c>
       <c r="C32">
-        <v>91.68853709749023</v>
+        <v>90.9404634141892</v>
       </c>
       <c r="D32">
-        <v>118.4685370974902</v>
+        <v>118.8454634141892</v>
       </c>
       <c r="E32">
-        <v>21.25</v>
+        <v>22.375</v>
       </c>
       <c r="F32">
-        <v>33.75</v>
+        <v>34.875</v>
       </c>
       <c r="G32">
         <v>6.97</v>
@@ -3911,28 +3911,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M32">
-        <v>1.697625</v>
+        <v>1.7542125</v>
       </c>
       <c r="N32">
-        <v>26.24115051020408</v>
+        <v>26.18456301020408</v>
       </c>
       <c r="O32">
-        <v>6.560287627551021</v>
+        <v>6.54614075255102</v>
       </c>
       <c r="P32">
-        <v>19.68086288265306</v>
+        <v>19.63842225765306</v>
       </c>
       <c r="Q32">
-        <v>23.68086288265306</v>
+        <v>23.63842225765306</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2185027832039005</v>
+        <v>0.2205321931122895</v>
       </c>
       <c r="T32">
-        <v>1.056228723217207</v>
+        <v>1.068640341586386</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>16.45756601735017</v>
+        <v>15.92667679098403</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1638619632474797</v>
+        <v>0.1634544782522291</v>
       </c>
       <c r="C33">
-        <v>90.9404634141892</v>
+        <v>90.19479588738449</v>
       </c>
       <c r="D33">
-        <v>118.8454634141892</v>
+        <v>119.2247958873845</v>
       </c>
       <c r="E33">
-        <v>22.375</v>
+        <v>23.5</v>
       </c>
       <c r="F33">
-        <v>34.875</v>
+        <v>36</v>
       </c>
       <c r="G33">
         <v>6.97</v>
@@ -3993,28 +3993,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M33">
-        <v>1.7542125</v>
+        <v>1.8108</v>
       </c>
       <c r="N33">
-        <v>26.18456301020408</v>
+        <v>26.12797551020408</v>
       </c>
       <c r="O33">
-        <v>6.54614075255102</v>
+        <v>6.53199387755102</v>
       </c>
       <c r="P33">
-        <v>19.63842225765306</v>
+        <v>19.59598163265306</v>
       </c>
       <c r="Q33">
-        <v>23.63842225765306</v>
+        <v>23.59598163265306</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2205321931122895</v>
+        <v>0.2226212915473958</v>
       </c>
       <c r="T33">
-        <v>1.068640341586386</v>
+        <v>1.08141700755466</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>15.92667679098403</v>
+        <v>15.42896814126578</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1634544782522291</v>
+        <v>0.1630469932569785</v>
       </c>
       <c r="C34">
-        <v>90.19479588738449</v>
+        <v>89.45155763085437</v>
       </c>
       <c r="D34">
-        <v>119.2247958873845</v>
+        <v>119.6065576308544</v>
       </c>
       <c r="E34">
-        <v>23.5</v>
+        <v>24.625</v>
       </c>
       <c r="F34">
-        <v>36</v>
+        <v>37.125</v>
       </c>
       <c r="G34">
         <v>6.97</v>
@@ -4075,28 +4075,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M34">
-        <v>1.8108</v>
+        <v>1.8673875</v>
       </c>
       <c r="N34">
-        <v>26.12797551020408</v>
+        <v>26.07138801020408</v>
       </c>
       <c r="O34">
-        <v>6.53199387755102</v>
+        <v>6.51784700255102</v>
       </c>
       <c r="P34">
-        <v>19.59598163265306</v>
+        <v>19.55354100765306</v>
       </c>
       <c r="Q34">
-        <v>23.59598163265306</v>
+        <v>23.55354100765306</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2226212915473958</v>
+        <v>0.2247727511298187</v>
       </c>
       <c r="T34">
-        <v>1.08141700755466</v>
+        <v>1.094575066536912</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>15.42896814126578</v>
+        <v>14.96142365213652</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1630469932569785</v>
+        <v>0.1626395082617279</v>
       </c>
       <c r="C35">
-        <v>89.45155763085437</v>
+        <v>88.71077205537243</v>
       </c>
       <c r="D35">
-        <v>119.6065576308544</v>
+        <v>119.9907720553724</v>
       </c>
       <c r="E35">
-        <v>24.625</v>
+        <v>25.75</v>
       </c>
       <c r="F35">
-        <v>37.125</v>
+        <v>38.25</v>
       </c>
       <c r="G35">
         <v>6.97</v>
@@ -4157,28 +4157,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M35">
-        <v>1.8673875</v>
+        <v>1.923975</v>
       </c>
       <c r="N35">
-        <v>26.07138801020408</v>
+        <v>26.01480051020408</v>
       </c>
       <c r="O35">
-        <v>6.51784700255102</v>
+        <v>6.503700127551021</v>
       </c>
       <c r="P35">
-        <v>19.55354100765306</v>
+        <v>19.51110038265306</v>
       </c>
       <c r="Q35">
-        <v>23.55354100765306</v>
+        <v>23.51110038265306</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2247727511298187</v>
+        <v>0.2269894064571635</v>
       </c>
       <c r="T35">
-        <v>1.094575066536912</v>
+        <v>1.108131854579232</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>14.96142365213652</v>
+        <v>14.52138178001486</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1626395082617279</v>
+        <v>0.1622320232664772</v>
       </c>
       <c r="C36">
-        <v>88.71077205537243</v>
+        <v>87.97246287349321</v>
       </c>
       <c r="D36">
-        <v>119.9907720553724</v>
+        <v>120.3774628734932</v>
       </c>
       <c r="E36">
-        <v>25.75</v>
+        <v>26.87500000000001</v>
       </c>
       <c r="F36">
-        <v>38.25</v>
+        <v>39.37500000000001</v>
       </c>
       <c r="G36">
         <v>6.97</v>
@@ -4239,28 +4239,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M36">
-        <v>1.923975</v>
+        <v>1.9805625</v>
       </c>
       <c r="N36">
-        <v>26.01480051020408</v>
+        <v>25.95821301020408</v>
       </c>
       <c r="O36">
-        <v>6.503700127551021</v>
+        <v>6.48955325255102</v>
       </c>
       <c r="P36">
-        <v>19.51110038265306</v>
+        <v>19.46865975765306</v>
       </c>
       <c r="Q36">
-        <v>23.51110038265306</v>
+        <v>23.46865975765306</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2269894064571635</v>
+        <v>0.2292742665638112</v>
       </c>
       <c r="T36">
-        <v>1.108131854579232</v>
+        <v>1.122105774561315</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>14.52138178001486</v>
+        <v>14.10648515772871</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1622320232664772</v>
+        <v>0.1618245382712266</v>
       </c>
       <c r="C37">
-        <v>87.97246287349321</v>
+        <v>87.23665410443056</v>
       </c>
       <c r="D37">
-        <v>120.3774628734932</v>
+        <v>120.7666541044306</v>
       </c>
       <c r="E37">
-        <v>26.87500000000001</v>
+        <v>28.00000000000001</v>
       </c>
       <c r="F37">
-        <v>39.37500000000001</v>
+        <v>40.50000000000001</v>
       </c>
       <c r="G37">
         <v>6.97</v>
@@ -4321,28 +4321,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M37">
-        <v>1.9805625</v>
+        <v>2.03715</v>
       </c>
       <c r="N37">
-        <v>25.95821301020408</v>
+        <v>25.90162551020408</v>
       </c>
       <c r="O37">
-        <v>6.48955325255102</v>
+        <v>6.47540637755102</v>
       </c>
       <c r="P37">
-        <v>19.46865975765306</v>
+        <v>19.42621913265306</v>
       </c>
       <c r="Q37">
-        <v>23.46865975765306</v>
+        <v>23.42621913265306</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2292742665638112</v>
+        <v>0.2316305285487916</v>
       </c>
       <c r="T37">
-        <v>1.122105774561315</v>
+        <v>1.136516379542839</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>14.10648515772871</v>
+        <v>13.71463834779181</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1618245382712266</v>
+        <v>0.161417053275976</v>
       </c>
       <c r="C38">
-        <v>87.23665410443051</v>
+        <v>86.50337007903101</v>
       </c>
       <c r="D38">
-        <v>120.7666541044305</v>
+        <v>121.158370079031</v>
       </c>
       <c r="E38">
-        <v>28</v>
+        <v>29.125</v>
       </c>
       <c r="F38">
-        <v>40.5</v>
+        <v>41.625</v>
       </c>
       <c r="G38">
         <v>6.97</v>
@@ -4403,28 +4403,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M38">
-        <v>2.03715</v>
+        <v>2.0937375</v>
       </c>
       <c r="N38">
-        <v>25.90162551020408</v>
+        <v>25.84503801020408</v>
       </c>
       <c r="O38">
-        <v>6.47540637755102</v>
+        <v>6.46125950255102</v>
       </c>
       <c r="P38">
-        <v>19.42621913265306</v>
+        <v>19.38377850765306</v>
       </c>
       <c r="Q38">
-        <v>23.42621913265306</v>
+        <v>23.38377850765306</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2316305285487916</v>
+        <v>0.2340615925015492</v>
       </c>
       <c r="T38">
-        <v>1.136516379542839</v>
+        <v>1.151384464047585</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>13.71463834779181</v>
+        <v>13.34397244650014</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.161417053275976</v>
+        <v>0.1610095682807254</v>
       </c>
       <c r="C39">
-        <v>86.50337007903101</v>
+        <v>85.77263544484427</v>
       </c>
       <c r="D39">
-        <v>121.158370079031</v>
+        <v>121.5526354448443</v>
       </c>
       <c r="E39">
-        <v>29.125</v>
+        <v>30.25</v>
       </c>
       <c r="F39">
-        <v>41.625</v>
+        <v>42.75</v>
       </c>
       <c r="G39">
         <v>6.97</v>
@@ -4485,28 +4485,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M39">
-        <v>2.0937375</v>
+        <v>2.150325</v>
       </c>
       <c r="N39">
-        <v>25.84503801020408</v>
+        <v>25.78845051020408</v>
       </c>
       <c r="O39">
-        <v>6.46125950255102</v>
+        <v>6.447112627551021</v>
       </c>
       <c r="P39">
-        <v>19.38377850765306</v>
+        <v>19.34133788265306</v>
       </c>
       <c r="Q39">
-        <v>23.38377850765306</v>
+        <v>23.34133788265306</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2340615925015492</v>
+        <v>0.2365710778721377</v>
       </c>
       <c r="T39">
-        <v>1.151384464047585</v>
+        <v>1.166732164181518</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>13.34397244650014</v>
+        <v>12.9928152768554</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1610095682807254</v>
+        <v>0.1610408332854747</v>
       </c>
       <c r="C40">
-        <v>85.77263544484427</v>
+        <v>84.6172938753291</v>
       </c>
       <c r="D40">
-        <v>121.5526354448443</v>
+        <v>121.5222938753291</v>
       </c>
       <c r="E40">
-        <v>30.25</v>
+        <v>31.375</v>
       </c>
       <c r="F40">
-        <v>42.75</v>
+        <v>43.875</v>
       </c>
       <c r="G40">
         <v>6.97</v>
@@ -4567,45 +4567,45 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M40">
-        <v>2.150325</v>
+        <v>2.272725</v>
       </c>
       <c r="N40">
-        <v>25.78845051020408</v>
+        <v>25.66605051020408</v>
       </c>
       <c r="O40">
-        <v>6.447112627551021</v>
+        <v>6.41651262755102</v>
       </c>
       <c r="P40">
-        <v>19.34133788265306</v>
+        <v>19.24953788265306</v>
       </c>
       <c r="Q40">
-        <v>23.34133788265306</v>
+        <v>23.24953788265306</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2365710778721377</v>
+        <v>0.239162841451598</v>
       </c>
       <c r="T40">
-        <v>1.166732164181518</v>
+        <v>1.182583067598529</v>
       </c>
       <c r="U40">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y40">
-        <v>12.9928152768554</v>
+        <v>12.29307351756331</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1610408332854747</v>
+        <v>0.1606445982902241</v>
       </c>
       <c r="C41">
-        <v>84.6172938753291</v>
+        <v>83.87794981186462</v>
       </c>
       <c r="D41">
-        <v>121.5222938753291</v>
+        <v>121.9079498118646</v>
       </c>
       <c r="E41">
-        <v>31.375</v>
+        <v>32.5</v>
       </c>
       <c r="F41">
-        <v>43.875</v>
+        <v>45</v>
       </c>
       <c r="G41">
         <v>6.97</v>
@@ -4649,28 +4649,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M41">
-        <v>2.272725</v>
+        <v>2.331</v>
       </c>
       <c r="N41">
-        <v>25.66605051020408</v>
+        <v>25.60777551020408</v>
       </c>
       <c r="O41">
-        <v>6.41651262755102</v>
+        <v>6.40194387755102</v>
       </c>
       <c r="P41">
-        <v>19.24953788265306</v>
+        <v>19.20583163265306</v>
       </c>
       <c r="Q41">
-        <v>23.24953788265306</v>
+        <v>23.20583163265306</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.239162841451598</v>
+        <v>0.2418409971503736</v>
       </c>
       <c r="T41">
-        <v>1.182583067598529</v>
+        <v>1.198962334462775</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>12.29307351756331</v>
+        <v>11.98574667962423</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1606445982902241</v>
+        <v>0.1602483632949735</v>
       </c>
       <c r="C42">
-        <v>83.87794981186462</v>
+        <v>83.14106133085514</v>
       </c>
       <c r="D42">
-        <v>121.9079498118646</v>
+        <v>122.2960613308551</v>
       </c>
       <c r="E42">
-        <v>32.5</v>
+        <v>33.625</v>
       </c>
       <c r="F42">
-        <v>45</v>
+        <v>46.125</v>
       </c>
       <c r="G42">
         <v>6.97</v>
@@ -4731,28 +4731,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M42">
-        <v>2.331</v>
+        <v>2.389275</v>
       </c>
       <c r="N42">
-        <v>25.60777551020408</v>
+        <v>25.54950051020408</v>
       </c>
       <c r="O42">
-        <v>6.40194387755102</v>
+        <v>6.38737512755102</v>
       </c>
       <c r="P42">
-        <v>19.20583163265306</v>
+        <v>19.16212538265306</v>
       </c>
       <c r="Q42">
-        <v>23.20583163265306</v>
+        <v>23.16212538265306</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2418409971503736</v>
+        <v>0.2446099377880907</v>
       </c>
       <c r="T42">
-        <v>1.198962334462775</v>
+        <v>1.215896830712249</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>11.98574667962423</v>
+        <v>11.69341139475535</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1602483632949735</v>
+        <v>0.1598521282997229</v>
       </c>
       <c r="C43">
-        <v>83.14106133085514</v>
+        <v>82.4066519603067</v>
       </c>
       <c r="D43">
-        <v>122.2960613308551</v>
+        <v>122.6866519603067</v>
       </c>
       <c r="E43">
-        <v>33.625</v>
+        <v>34.75000000000001</v>
       </c>
       <c r="F43">
-        <v>46.125</v>
+        <v>47.25000000000001</v>
       </c>
       <c r="G43">
         <v>6.97</v>
@@ -4813,28 +4813,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M43">
-        <v>2.389275</v>
+        <v>2.44755</v>
       </c>
       <c r="N43">
-        <v>25.54950051020408</v>
+        <v>25.49122551020408</v>
       </c>
       <c r="O43">
-        <v>6.38737512755102</v>
+        <v>6.37280637755102</v>
       </c>
       <c r="P43">
-        <v>19.16212538265306</v>
+        <v>19.11841913265306</v>
       </c>
       <c r="Q43">
-        <v>23.16212538265306</v>
+        <v>23.11841913265306</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2446099377880907</v>
+        <v>0.2474743591374533</v>
       </c>
       <c r="T43">
-        <v>1.215896830712249</v>
+        <v>1.233415275108257</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>11.69341139475535</v>
+        <v>11.41499683773736</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1598521282997229</v>
+        <v>0.1594558933044723</v>
       </c>
       <c r="C44">
-        <v>82.40665196030668</v>
+        <v>81.67474552976483</v>
       </c>
       <c r="D44">
-        <v>122.6866519603067</v>
+        <v>123.0797455297648</v>
       </c>
       <c r="E44">
-        <v>34.75</v>
+        <v>35.875</v>
       </c>
       <c r="F44">
-        <v>47.25</v>
+        <v>48.375</v>
       </c>
       <c r="G44">
         <v>6.97</v>
@@ -4895,28 +4895,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M44">
-        <v>2.44755</v>
+        <v>2.505825</v>
       </c>
       <c r="N44">
-        <v>25.49122551020408</v>
+        <v>25.43295051020408</v>
       </c>
       <c r="O44">
-        <v>6.37280637755102</v>
+        <v>6.35823762755102</v>
       </c>
       <c r="P44">
-        <v>19.11841913265306</v>
+        <v>19.07471288265306</v>
       </c>
       <c r="Q44">
-        <v>23.11841913265306</v>
+        <v>23.07471288265306</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2474743591374533</v>
+        <v>0.2504392864990742</v>
       </c>
       <c r="T44">
-        <v>1.233415275108257</v>
+        <v>1.251548401763774</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>11.41499683773736</v>
+        <v>11.14953179499928</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1594558933044723</v>
+        <v>0.1590596583092217</v>
       </c>
       <c r="C45">
-        <v>81.67474552976483</v>
+        <v>80.94536617516025</v>
       </c>
       <c r="D45">
-        <v>123.0797455297648</v>
+        <v>123.4753661751602</v>
       </c>
       <c r="E45">
-        <v>35.875</v>
+        <v>37</v>
       </c>
       <c r="F45">
-        <v>48.375</v>
+        <v>49.5</v>
       </c>
       <c r="G45">
         <v>6.97</v>
@@ -4977,28 +4977,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M45">
-        <v>2.505825</v>
+        <v>2.5641</v>
       </c>
       <c r="N45">
-        <v>25.43295051020408</v>
+        <v>25.37467551020408</v>
       </c>
       <c r="O45">
-        <v>6.35823762755102</v>
+        <v>6.34366887755102</v>
       </c>
       <c r="P45">
-        <v>19.07471288265306</v>
+        <v>19.03100663265306</v>
       </c>
       <c r="Q45">
-        <v>23.07471288265306</v>
+        <v>23.03100663265306</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2504392864990742</v>
+        <v>0.2535101041236101</v>
       </c>
       <c r="T45">
-        <v>1.251548401763774</v>
+        <v>1.270329140085559</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>11.14953179499928</v>
+        <v>10.89613334511294</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1590596583092217</v>
+        <v>0.158663423313971</v>
       </c>
       <c r="C46">
-        <v>80.94536617516025</v>
+        <v>80.21853834374926</v>
       </c>
       <c r="D46">
-        <v>123.4753661751602</v>
+        <v>123.8735383437493</v>
       </c>
       <c r="E46">
-        <v>37</v>
+        <v>38.125</v>
       </c>
       <c r="F46">
-        <v>49.5</v>
+        <v>50.625</v>
       </c>
       <c r="G46">
         <v>6.97</v>
@@ -5059,28 +5059,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M46">
-        <v>2.5641</v>
+        <v>2.622375</v>
       </c>
       <c r="N46">
-        <v>25.37467551020408</v>
+        <v>25.31640051020408</v>
       </c>
       <c r="O46">
-        <v>6.34366887755102</v>
+        <v>6.329100127551021</v>
       </c>
       <c r="P46">
-        <v>19.03100663265306</v>
+        <v>18.98730038265306</v>
       </c>
       <c r="Q46">
-        <v>23.03100663265306</v>
+        <v>22.98730038265306</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2535101041236101</v>
+        <v>0.2566925878435837</v>
       </c>
       <c r="T46">
-        <v>1.270329140085559</v>
+        <v>1.289792814346318</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>10.89613334511294</v>
+        <v>10.65399704855487</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.158663423313971</v>
+        <v>0.1582671883187204</v>
       </c>
       <c r="C47">
-        <v>80.21853834374926</v>
+        <v>79.49428679914948</v>
       </c>
       <c r="D47">
-        <v>123.8735383437493</v>
+        <v>124.2742867991495</v>
       </c>
       <c r="E47">
-        <v>38.125</v>
+        <v>39.25</v>
       </c>
       <c r="F47">
-        <v>50.625</v>
+        <v>51.75</v>
       </c>
       <c r="G47">
         <v>6.97</v>
@@ -5141,28 +5141,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M47">
-        <v>2.622375</v>
+        <v>2.68065</v>
       </c>
       <c r="N47">
-        <v>25.31640051020408</v>
+        <v>25.25812551020408</v>
       </c>
       <c r="O47">
-        <v>6.329100127551021</v>
+        <v>6.31453137755102</v>
       </c>
       <c r="P47">
-        <v>18.98730038265306</v>
+        <v>18.94359413265306</v>
       </c>
       <c r="Q47">
-        <v>22.98730038265306</v>
+        <v>22.94359413265306</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2566925878435837</v>
+        <v>0.2599929413309637</v>
       </c>
       <c r="T47">
-        <v>1.289792814346318</v>
+        <v>1.309977365431551</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>10.65399704855487</v>
+        <v>10.42238841706455</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1582671883187204</v>
+        <v>0.1578709533234698</v>
       </c>
       <c r="C48">
-        <v>79.49428679914948</v>
+        <v>78.77263662647383</v>
       </c>
       <c r="D48">
-        <v>124.2742867991495</v>
+        <v>124.6776366264738</v>
       </c>
       <c r="E48">
-        <v>39.25</v>
+        <v>40.375</v>
       </c>
       <c r="F48">
-        <v>51.75</v>
+        <v>52.875</v>
       </c>
       <c r="G48">
         <v>6.97</v>
@@ -5223,28 +5223,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M48">
-        <v>2.68065</v>
+        <v>2.738925</v>
       </c>
       <c r="N48">
-        <v>25.25812551020408</v>
+        <v>25.19985051020408</v>
       </c>
       <c r="O48">
-        <v>6.31453137755102</v>
+        <v>6.29996262755102</v>
       </c>
       <c r="P48">
-        <v>18.94359413265306</v>
+        <v>18.89988788265306</v>
       </c>
       <c r="Q48">
-        <v>22.94359413265306</v>
+        <v>22.89988788265306</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2599929413309637</v>
+        <v>0.2634178364593769</v>
       </c>
       <c r="T48">
-        <v>1.309977365431551</v>
+        <v>1.33092359768981</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>10.42238841706455</v>
+        <v>10.20063547202062</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1578709533234698</v>
+        <v>0.1574747183282192</v>
       </c>
       <c r="C49">
-        <v>78.77263662647383</v>
+        <v>78.05361323756489</v>
       </c>
       <c r="D49">
-        <v>124.6776366264738</v>
+        <v>125.0836132375649</v>
       </c>
       <c r="E49">
-        <v>40.375</v>
+        <v>41.50000000000001</v>
       </c>
       <c r="F49">
-        <v>52.875</v>
+        <v>54.00000000000001</v>
       </c>
       <c r="G49">
         <v>6.97</v>
@@ -5305,28 +5305,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M49">
-        <v>2.738925</v>
+        <v>2.7972</v>
       </c>
       <c r="N49">
-        <v>25.19985051020408</v>
+        <v>25.14157551020408</v>
       </c>
       <c r="O49">
-        <v>6.29996262755102</v>
+        <v>6.28539387755102</v>
       </c>
       <c r="P49">
-        <v>18.89988788265306</v>
+        <v>18.85618163265306</v>
       </c>
       <c r="Q49">
-        <v>22.89988788265306</v>
+        <v>22.85618163265306</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2634178364593769</v>
+        <v>0.2669744583234984</v>
       </c>
       <c r="T49">
-        <v>1.33092359768981</v>
+        <v>1.352675454265695</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>10.20063547202062</v>
+        <v>9.988122233020192</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1574747183282192</v>
+        <v>0.1577032333329685</v>
       </c>
       <c r="C50">
-        <v>78.05361323756489</v>
+        <v>76.69415798713035</v>
       </c>
       <c r="D50">
-        <v>125.0836132375649</v>
+        <v>124.8491579871304</v>
       </c>
       <c r="E50">
-        <v>41.5</v>
+        <v>42.625</v>
       </c>
       <c r="F50">
-        <v>54</v>
+        <v>55.125</v>
       </c>
       <c r="G50">
         <v>6.97</v>
@@ -5387,45 +5387,45 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M50">
-        <v>2.7972</v>
+        <v>2.9491875</v>
       </c>
       <c r="N50">
-        <v>25.14157551020408</v>
+        <v>24.98958801020408</v>
       </c>
       <c r="O50">
-        <v>6.28539387755102</v>
+        <v>6.24739700255102</v>
       </c>
       <c r="P50">
-        <v>18.85618163265306</v>
+        <v>18.74219100765306</v>
       </c>
       <c r="Q50">
-        <v>22.85618163265306</v>
+        <v>22.74219100765306</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2669744583234984</v>
+        <v>0.2706705555548403</v>
       </c>
       <c r="T50">
-        <v>1.352675454265695</v>
+        <v>1.375280324824948</v>
       </c>
       <c r="U50">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>9.988122233020192</v>
+        <v>9.473380553187644</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1577032333329685</v>
+        <v>0.1573197483377179</v>
       </c>
       <c r="C51">
-        <v>76.69415798713035</v>
+        <v>75.96311338346842</v>
       </c>
       <c r="D51">
-        <v>124.8491579871304</v>
+        <v>125.2431133834684</v>
       </c>
       <c r="E51">
-        <v>42.625</v>
+        <v>43.75</v>
       </c>
       <c r="F51">
-        <v>55.125</v>
+        <v>56.25</v>
       </c>
       <c r="G51">
         <v>6.97</v>
@@ -5469,28 +5469,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M51">
-        <v>2.9491875</v>
+        <v>3.009375</v>
       </c>
       <c r="N51">
-        <v>24.98958801020408</v>
+        <v>24.92940051020408</v>
       </c>
       <c r="O51">
-        <v>6.24739700255102</v>
+        <v>6.232350127551021</v>
       </c>
       <c r="P51">
-        <v>18.74219100765306</v>
+        <v>18.69705038265306</v>
       </c>
       <c r="Q51">
-        <v>22.74219100765306</v>
+        <v>22.69705038265306</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2706705555548403</v>
+        <v>0.2745144966754358</v>
       </c>
       <c r="T51">
-        <v>1.375280324824948</v>
+        <v>1.398789390206571</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>9.473380553187644</v>
+        <v>9.283912942123891</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1573197483377179</v>
+        <v>0.1569362633424673</v>
       </c>
       <c r="C52">
-        <v>75.96311338346842</v>
+        <v>75.23456286363862</v>
       </c>
       <c r="D52">
-        <v>125.2431133834684</v>
+        <v>125.6395628636386</v>
       </c>
       <c r="E52">
-        <v>43.75</v>
+        <v>44.875</v>
       </c>
       <c r="F52">
-        <v>56.25</v>
+        <v>57.375</v>
       </c>
       <c r="G52">
         <v>6.97</v>
@@ -5551,28 +5551,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M52">
-        <v>3.009375</v>
+        <v>3.0695625</v>
       </c>
       <c r="N52">
-        <v>24.92940051020408</v>
+        <v>24.86921301020408</v>
       </c>
       <c r="O52">
-        <v>6.232350127551021</v>
+        <v>6.21730325255102</v>
       </c>
       <c r="P52">
-        <v>18.69705038265306</v>
+        <v>18.65190975765306</v>
       </c>
       <c r="Q52">
-        <v>22.69705038265306</v>
+        <v>22.65190975765306</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2745144966754358</v>
+        <v>0.2785153333519741</v>
       </c>
       <c r="T52">
-        <v>1.398789390206571</v>
+        <v>1.42325800927724</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>9.283912942123891</v>
+        <v>9.101875433454794</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1569362633424673</v>
+        <v>0.1565527783472166</v>
       </c>
       <c r="C53">
-        <v>75.23456286363862</v>
+        <v>74.50853018746463</v>
       </c>
       <c r="D53">
-        <v>125.6395628636386</v>
+        <v>126.0385301874646</v>
       </c>
       <c r="E53">
-        <v>44.875</v>
+        <v>46</v>
       </c>
       <c r="F53">
-        <v>57.375</v>
+        <v>58.5</v>
       </c>
       <c r="G53">
         <v>6.97</v>
@@ -5633,28 +5633,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M53">
-        <v>3.0695625</v>
+        <v>3.12975</v>
       </c>
       <c r="N53">
-        <v>24.86921301020408</v>
+        <v>24.80902551020408</v>
       </c>
       <c r="O53">
-        <v>6.21730325255102</v>
+        <v>6.20225637755102</v>
       </c>
       <c r="P53">
-        <v>18.65190975765306</v>
+        <v>18.60676913265306</v>
       </c>
       <c r="Q53">
-        <v>22.65190975765306</v>
+        <v>22.60676913265306</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2785153333519741</v>
+        <v>0.2826828715567014</v>
       </c>
       <c r="T53">
-        <v>1.42325800927724</v>
+        <v>1.44874615414252</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>9.101875433454794</v>
+        <v>8.926839367426817</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1565527783472166</v>
+        <v>0.1561692933519661</v>
       </c>
       <c r="C54">
-        <v>74.50853018746463</v>
+        <v>73.78503941752783</v>
       </c>
       <c r="D54">
-        <v>126.0385301874646</v>
+        <v>126.4400394175278</v>
       </c>
       <c r="E54">
-        <v>46</v>
+        <v>47.125</v>
       </c>
       <c r="F54">
-        <v>58.5</v>
+        <v>59.625</v>
       </c>
       <c r="G54">
         <v>6.97</v>
@@ -5715,28 +5715,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M54">
-        <v>3.12975</v>
+        <v>3.1899375</v>
       </c>
       <c r="N54">
-        <v>24.80902551020408</v>
+        <v>24.74883801020408</v>
       </c>
       <c r="O54">
-        <v>6.20225637755102</v>
+        <v>6.187209502551021</v>
       </c>
       <c r="P54">
-        <v>18.60676913265306</v>
+        <v>18.56162850765306</v>
       </c>
       <c r="Q54">
-        <v>22.60676913265306</v>
+        <v>22.56162850765306</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2826828715567014</v>
+        <v>0.2870277518126937</v>
       </c>
       <c r="T54">
-        <v>1.44874615414252</v>
+        <v>1.475318900916961</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>8.926839367426817</v>
+        <v>8.758408435965933</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1561692933519661</v>
+        <v>0.1557858083567154</v>
       </c>
       <c r="C55">
-        <v>73.78503941752783</v>
+        <v>73.06411492400542</v>
       </c>
       <c r="D55">
-        <v>126.4400394175278</v>
+        <v>126.8441149240054</v>
       </c>
       <c r="E55">
-        <v>47.125</v>
+        <v>48.25000000000001</v>
       </c>
       <c r="F55">
-        <v>59.625</v>
+        <v>60.75000000000001</v>
       </c>
       <c r="G55">
         <v>6.97</v>
@@ -5797,28 +5797,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M55">
-        <v>3.1899375</v>
+        <v>3.250125</v>
       </c>
       <c r="N55">
-        <v>24.74883801020408</v>
+        <v>24.68865051020408</v>
       </c>
       <c r="O55">
-        <v>6.187209502551021</v>
+        <v>6.17216262755102</v>
       </c>
       <c r="P55">
-        <v>18.56162850765306</v>
+        <v>18.51648788265306</v>
       </c>
       <c r="Q55">
-        <v>22.56162850765306</v>
+        <v>22.51648788265306</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2870277518126937</v>
+        <v>0.2915615399059031</v>
       </c>
       <c r="T55">
-        <v>1.475318900916961</v>
+        <v>1.503046984507682</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>8.758408435965933</v>
+        <v>8.59621568715175</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1557858083567154</v>
+        <v>0.1554023233614648</v>
       </c>
       <c r="C56">
-        <v>73.06411492400542</v>
+        <v>72.34578138960089</v>
       </c>
       <c r="D56">
-        <v>126.8441149240054</v>
+        <v>127.2507813896009</v>
       </c>
       <c r="E56">
-        <v>48.25000000000001</v>
+        <v>49.37500000000001</v>
       </c>
       <c r="F56">
-        <v>60.75000000000001</v>
+        <v>61.87500000000001</v>
       </c>
       <c r="G56">
         <v>6.97</v>
@@ -5879,28 +5879,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M56">
-        <v>3.250125</v>
+        <v>3.3103125</v>
       </c>
       <c r="N56">
-        <v>24.68865051020408</v>
+        <v>24.62846301020408</v>
       </c>
       <c r="O56">
-        <v>6.17216262755102</v>
+        <v>6.15711575255102</v>
       </c>
       <c r="P56">
-        <v>18.51648788265306</v>
+        <v>18.47134725765306</v>
       </c>
       <c r="Q56">
-        <v>22.51648788265306</v>
+        <v>22.47134725765306</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2915615399059031</v>
+        <v>0.296296829692144</v>
       </c>
       <c r="T56">
-        <v>1.503046984507682</v>
+        <v>1.532007427369102</v>
       </c>
       <c r="U56">
         <v>0.0535</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>8.59621568715175</v>
+        <v>8.439920856476263</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1554023233614648</v>
+        <v>0.1550188383662142</v>
       </c>
       <c r="C57">
-        <v>72.34578138960089</v>
+        <v>71.63006381457001</v>
       </c>
       <c r="D57">
-        <v>127.2507813896009</v>
+        <v>127.66006381457</v>
       </c>
       <c r="E57">
-        <v>49.37500000000001</v>
+        <v>50.50000000000001</v>
       </c>
       <c r="F57">
-        <v>61.87500000000001</v>
+        <v>63.00000000000001</v>
       </c>
       <c r="G57">
         <v>6.97</v>
@@ -5961,28 +5961,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M57">
-        <v>3.3103125</v>
+        <v>3.3705</v>
       </c>
       <c r="N57">
-        <v>24.62846301020408</v>
+        <v>24.56827551020408</v>
       </c>
       <c r="O57">
-        <v>6.15711575255102</v>
+        <v>6.14206887755102</v>
       </c>
       <c r="P57">
-        <v>18.47134725765306</v>
+        <v>18.42620663265306</v>
       </c>
       <c r="Q57">
-        <v>22.47134725765306</v>
+        <v>22.42620663265306</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.296296829692144</v>
+        <v>0.3012473599232141</v>
       </c>
       <c r="T57">
-        <v>1.532007427369102</v>
+        <v>1.562284253996949</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>8.439920856476263</v>
+        <v>8.289207984039187</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1550188383662142</v>
+        <v>0.1546353533709636</v>
       </c>
       <c r="C58">
-        <v>71.63006381457001</v>
+        <v>70.91698752184428</v>
       </c>
       <c r="D58">
-        <v>127.66006381457</v>
+        <v>128.0719875218443</v>
       </c>
       <c r="E58">
-        <v>50.50000000000001</v>
+        <v>51.625</v>
       </c>
       <c r="F58">
-        <v>63.00000000000001</v>
+        <v>64.125</v>
       </c>
       <c r="G58">
         <v>6.97</v>
@@ -6043,28 +6043,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M58">
-        <v>3.3705</v>
+        <v>3.4306875</v>
       </c>
       <c r="N58">
-        <v>24.56827551020408</v>
+        <v>24.50808801020408</v>
       </c>
       <c r="O58">
-        <v>6.14206887755102</v>
+        <v>6.12702200255102</v>
       </c>
       <c r="P58">
-        <v>18.42620663265306</v>
+        <v>18.38106600765306</v>
       </c>
       <c r="Q58">
-        <v>22.42620663265306</v>
+        <v>22.38106600765306</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3012473599232141</v>
+        <v>0.3064281473743339</v>
       </c>
       <c r="T58">
-        <v>1.562284253996949</v>
+        <v>1.593969305119116</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>8.289207984039187</v>
+        <v>8.143783282564815</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1546353533709636</v>
+        <v>0.1542518683757129</v>
       </c>
       <c r="C59">
-        <v>70.91698752184428</v>
+        <v>70.20657816225365</v>
       </c>
       <c r="D59">
-        <v>128.0719875218443</v>
+        <v>128.4865781622537</v>
       </c>
       <c r="E59">
-        <v>51.625</v>
+        <v>52.75000000000001</v>
       </c>
       <c r="F59">
-        <v>64.125</v>
+        <v>65.25000000000001</v>
       </c>
       <c r="G59">
         <v>6.97</v>
@@ -6125,28 +6125,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M59">
-        <v>3.4306875</v>
+        <v>3.490875000000001</v>
       </c>
       <c r="N59">
-        <v>24.50808801020408</v>
+        <v>24.44790051020408</v>
       </c>
       <c r="O59">
-        <v>6.12702200255102</v>
+        <v>6.11197512755102</v>
       </c>
       <c r="P59">
-        <v>18.38106600765306</v>
+        <v>18.33592538265306</v>
       </c>
       <c r="Q59">
-        <v>22.38106600765306</v>
+        <v>22.33592538265306</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3064281473743339</v>
+        <v>0.3118556389897927</v>
       </c>
       <c r="T59">
-        <v>1.593969305119116</v>
+        <v>1.627163168199481</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>8.143783282564815</v>
+        <v>8.003373225968868</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1542518683757129</v>
+        <v>0.1538683833804623</v>
       </c>
       <c r="C60">
-        <v>70.20657816225363</v>
+        <v>69.49886171985099</v>
       </c>
       <c r="D60">
-        <v>128.4865781622536</v>
+        <v>128.903861719851</v>
       </c>
       <c r="E60">
-        <v>52.75</v>
+        <v>53.875</v>
       </c>
       <c r="F60">
-        <v>65.25</v>
+        <v>66.375</v>
       </c>
       <c r="G60">
         <v>6.97</v>
@@ -6207,28 +6207,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M60">
-        <v>3.490875</v>
+        <v>3.5510625</v>
       </c>
       <c r="N60">
-        <v>24.44790051020408</v>
+        <v>24.38771301020408</v>
       </c>
       <c r="O60">
-        <v>6.111975127551021</v>
+        <v>6.09692825255102</v>
       </c>
       <c r="P60">
-        <v>18.33592538265306</v>
+        <v>18.29078475765306</v>
       </c>
       <c r="Q60">
-        <v>22.33592538265306</v>
+        <v>22.29078475765306</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3118556389897927</v>
+        <v>0.3175478862938105</v>
       </c>
       <c r="T60">
-        <v>1.62716316819948</v>
+        <v>1.661976244113033</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>8.003373225968872</v>
+        <v>7.867722832308381</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1538683833804623</v>
+        <v>0.1534848983852117</v>
       </c>
       <c r="C61">
-        <v>69.49886171985099</v>
+        <v>68.79386451734072</v>
       </c>
       <c r="D61">
-        <v>128.903861719851</v>
+        <v>129.3238645173407</v>
       </c>
       <c r="E61">
-        <v>53.875</v>
+        <v>55</v>
       </c>
       <c r="F61">
-        <v>66.375</v>
+        <v>67.5</v>
       </c>
       <c r="G61">
         <v>6.97</v>
@@ -6289,28 +6289,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M61">
-        <v>3.5510625</v>
+        <v>3.61125</v>
       </c>
       <c r="N61">
-        <v>24.38771301020408</v>
+        <v>24.32752551020408</v>
       </c>
       <c r="O61">
-        <v>6.09692825255102</v>
+        <v>6.081881377551021</v>
       </c>
       <c r="P61">
-        <v>18.29078475765306</v>
+        <v>18.24564413265306</v>
       </c>
       <c r="Q61">
-        <v>22.29078475765306</v>
+        <v>22.24564413265306</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3175478862938105</v>
+        <v>0.3235247459630292</v>
       </c>
       <c r="T61">
-        <v>1.661976244113033</v>
+        <v>1.698529973822265</v>
       </c>
       <c r="U61">
         <v>0.0535</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>7.867722832308381</v>
+        <v>7.736594118436575</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1534848983852117</v>
+        <v>0.1534674133899611</v>
       </c>
       <c r="C62">
-        <v>68.79386451734072</v>
+        <v>67.68807979195162</v>
       </c>
       <c r="D62">
-        <v>129.3238645173407</v>
+        <v>129.3430797919516</v>
       </c>
       <c r="E62">
-        <v>55</v>
+        <v>56.125</v>
       </c>
       <c r="F62">
-        <v>67.5</v>
+        <v>68.625</v>
       </c>
       <c r="G62">
         <v>6.97</v>
@@ -6371,45 +6371,45 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M62">
-        <v>3.61125</v>
+        <v>3.7263375</v>
       </c>
       <c r="N62">
-        <v>24.32752551020408</v>
+        <v>24.21243801020408</v>
       </c>
       <c r="O62">
-        <v>6.081881377551021</v>
+        <v>6.05310950255102</v>
       </c>
       <c r="P62">
-        <v>18.24564413265306</v>
+        <v>18.15932850765306</v>
       </c>
       <c r="Q62">
-        <v>22.24564413265306</v>
+        <v>22.15932850765306</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3235247459630292</v>
+        <v>0.3298081112563105</v>
       </c>
       <c r="T62">
-        <v>1.698529973822265</v>
+        <v>1.736958253772995</v>
       </c>
       <c r="U62">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V62">
         <v>0.25</v>
       </c>
       <c r="W62">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y62">
-        <v>7.736594118436575</v>
+        <v>7.497650309507414</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1534674133899611</v>
+        <v>0.1530899283947105</v>
       </c>
       <c r="C63">
-        <v>67.68807979195162</v>
+        <v>66.97931675711084</v>
       </c>
       <c r="D63">
-        <v>129.3430797919516</v>
+        <v>129.7593167571108</v>
       </c>
       <c r="E63">
-        <v>56.125</v>
+        <v>57.25</v>
       </c>
       <c r="F63">
-        <v>68.625</v>
+        <v>69.75</v>
       </c>
       <c r="G63">
         <v>6.97</v>
@@ -6453,28 +6453,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M63">
-        <v>3.7263375</v>
+        <v>3.787425</v>
       </c>
       <c r="N63">
-        <v>24.21243801020408</v>
+        <v>24.15135051020408</v>
       </c>
       <c r="O63">
-        <v>6.05310950255102</v>
+        <v>6.037837627551021</v>
       </c>
       <c r="P63">
-        <v>18.15932850765306</v>
+        <v>18.11351288265306</v>
       </c>
       <c r="Q63">
-        <v>22.15932850765306</v>
+        <v>22.11351288265306</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3298081112563105</v>
+        <v>0.3364221799860801</v>
       </c>
       <c r="T63">
-        <v>1.736958253772995</v>
+        <v>1.777409074773763</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>7.497650309507414</v>
+        <v>7.376720465805681</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1530899283947105</v>
+        <v>0.1527124433994598</v>
       </c>
       <c r="C64">
-        <v>66.97931675711084</v>
+        <v>66.27324134274326</v>
       </c>
       <c r="D64">
-        <v>129.7593167571108</v>
+        <v>130.1782413427433</v>
       </c>
       <c r="E64">
-        <v>57.25</v>
+        <v>58.375</v>
       </c>
       <c r="F64">
-        <v>69.75</v>
+        <v>70.875</v>
       </c>
       <c r="G64">
         <v>6.97</v>
@@ -6535,28 +6535,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M64">
-        <v>3.787425</v>
+        <v>3.8485125</v>
       </c>
       <c r="N64">
-        <v>24.15135051020408</v>
+        <v>24.09026301020408</v>
       </c>
       <c r="O64">
-        <v>6.037837627551021</v>
+        <v>6.022565752551021</v>
       </c>
       <c r="P64">
-        <v>18.11351288265306</v>
+        <v>18.06769725765306</v>
       </c>
       <c r="Q64">
-        <v>22.11351288265306</v>
+        <v>22.06769725765306</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3364221799860801</v>
+        <v>0.343393765944486</v>
       </c>
       <c r="T64">
-        <v>1.777409074773763</v>
+        <v>1.820046426639438</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>7.376720465805681</v>
+        <v>7.259629664761147</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1527124433994598</v>
+        <v>0.1523349584042092</v>
       </c>
       <c r="C65">
-        <v>66.27324134274326</v>
+        <v>65.56987966389946</v>
       </c>
       <c r="D65">
-        <v>130.1782413427433</v>
+        <v>130.5998796638995</v>
       </c>
       <c r="E65">
-        <v>58.375</v>
+        <v>59.5</v>
       </c>
       <c r="F65">
-        <v>70.875</v>
+        <v>72</v>
       </c>
       <c r="G65">
         <v>6.97</v>
@@ -6617,28 +6617,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M65">
-        <v>3.8485125</v>
+        <v>3.9096</v>
       </c>
       <c r="N65">
-        <v>24.09026301020408</v>
+        <v>24.02917551020408</v>
       </c>
       <c r="O65">
-        <v>6.022565752551021</v>
+        <v>6.00729387755102</v>
       </c>
       <c r="P65">
-        <v>18.06769725765306</v>
+        <v>18.02188163265306</v>
       </c>
       <c r="Q65">
-        <v>22.06769725765306</v>
+        <v>22.02188163265306</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.343393765944486</v>
+        <v>0.3507526622339145</v>
       </c>
       <c r="T65">
-        <v>1.820046426639438</v>
+        <v>1.865052520275428</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>7.259629664761147</v>
+        <v>7.146197951249253</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1523349584042092</v>
+        <v>0.1519574734089586</v>
       </c>
       <c r="C66">
-        <v>65.56987966389946</v>
+        <v>64.86925817506878</v>
       </c>
       <c r="D66">
-        <v>130.5998796638995</v>
+        <v>131.0242581750688</v>
       </c>
       <c r="E66">
-        <v>59.5</v>
+        <v>60.625</v>
       </c>
       <c r="F66">
-        <v>72</v>
+        <v>73.125</v>
       </c>
       <c r="G66">
         <v>6.97</v>
@@ -6699,28 +6699,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M66">
-        <v>3.9096</v>
+        <v>3.9706875</v>
       </c>
       <c r="N66">
-        <v>24.02917551020408</v>
+        <v>23.96808801020408</v>
       </c>
       <c r="O66">
-        <v>6.00729387755102</v>
+        <v>5.99202200255102</v>
       </c>
       <c r="P66">
-        <v>18.02188163265306</v>
+        <v>17.97606600765306</v>
       </c>
       <c r="Q66">
-        <v>22.02188163265306</v>
+        <v>21.97606600765306</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3507526622339145</v>
+        <v>0.3585320668827388</v>
       </c>
       <c r="T66">
-        <v>1.865052520275428</v>
+        <v>1.912630390690617</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>7.146197951249253</v>
+        <v>7.036256444306957</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1519574734089586</v>
+        <v>0.151579988413708</v>
       </c>
       <c r="C67">
-        <v>64.86925817506878</v>
+        <v>64.17140367571224</v>
       </c>
       <c r="D67">
-        <v>131.0242581750688</v>
+        <v>131.4514036757122</v>
       </c>
       <c r="E67">
-        <v>60.625</v>
+        <v>61.75</v>
       </c>
       <c r="F67">
-        <v>73.125</v>
+        <v>74.25</v>
       </c>
       <c r="G67">
         <v>6.97</v>
@@ -6781,28 +6781,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M67">
-        <v>3.9706875</v>
+        <v>4.031775</v>
       </c>
       <c r="N67">
-        <v>23.96808801020408</v>
+        <v>23.90700051020408</v>
       </c>
       <c r="O67">
-        <v>5.99202200255102</v>
+        <v>5.97675012755102</v>
       </c>
       <c r="P67">
-        <v>17.97606600765306</v>
+        <v>17.93025038265306</v>
       </c>
       <c r="Q67">
-        <v>21.97606600765306</v>
+        <v>21.93025038265306</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3585320668827388</v>
+        <v>0.3667690835697293</v>
       </c>
       <c r="T67">
-        <v>1.912630390690617</v>
+        <v>1.963006959365524</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>7.036256444306957</v>
+        <v>6.929646498181095</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.151579988413708</v>
+        <v>0.1512025034184573</v>
       </c>
       <c r="C68">
-        <v>64.17140367571224</v>
+        <v>63.47634331590416</v>
       </c>
       <c r="D68">
-        <v>131.4514036757122</v>
+        <v>131.8813433159042</v>
       </c>
       <c r="E68">
-        <v>61.75</v>
+        <v>62.875</v>
       </c>
       <c r="F68">
-        <v>74.25</v>
+        <v>75.375</v>
       </c>
       <c r="G68">
         <v>6.97</v>
@@ -6863,28 +6863,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M68">
-        <v>4.031775</v>
+        <v>4.0928625</v>
       </c>
       <c r="N68">
-        <v>23.90700051020408</v>
+        <v>23.84591301020408</v>
       </c>
       <c r="O68">
-        <v>5.97675012755102</v>
+        <v>5.961478252551021</v>
       </c>
       <c r="P68">
-        <v>17.93025038265306</v>
+        <v>17.88443475765306</v>
       </c>
       <c r="Q68">
-        <v>21.93025038265306</v>
+        <v>21.88443475765306</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3667690835697293</v>
+        <v>0.3755053133892647</v>
       </c>
       <c r="T68">
-        <v>1.963006959365524</v>
+        <v>2.016436653414667</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>6.929646498181095</v>
+        <v>6.82621893850675</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1512025034184573</v>
+        <v>0.1508250184232067</v>
       </c>
       <c r="C69">
-        <v>63.47634331590416</v>
+        <v>62.78410460208471</v>
       </c>
       <c r="D69">
-        <v>131.8813433159042</v>
+        <v>132.3141046020847</v>
       </c>
       <c r="E69">
-        <v>62.875</v>
+        <v>64</v>
       </c>
       <c r="F69">
-        <v>75.375</v>
+        <v>76.5</v>
       </c>
       <c r="G69">
         <v>6.97</v>
@@ -6945,28 +6945,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M69">
-        <v>4.0928625</v>
+        <v>4.15395</v>
       </c>
       <c r="N69">
-        <v>23.84591301020408</v>
+        <v>23.78482551020408</v>
       </c>
       <c r="O69">
-        <v>5.961478252551021</v>
+        <v>5.94620637755102</v>
       </c>
       <c r="P69">
-        <v>17.88443475765306</v>
+        <v>17.83861913265306</v>
       </c>
       <c r="Q69">
-        <v>21.88443475765306</v>
+        <v>21.83861913265306</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3755053133892647</v>
+        <v>0.384787557572521</v>
       </c>
       <c r="T69">
-        <v>2.016436653414667</v>
+        <v>2.073205703341882</v>
       </c>
       <c r="U69">
         <v>0.0543</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>6.82621893850675</v>
+        <v>6.72583336588165</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1508250184232067</v>
+        <v>0.1504475334279561</v>
       </c>
       <c r="C70">
-        <v>62.78410460208471</v>
+        <v>62.09471540292606</v>
       </c>
       <c r="D70">
-        <v>132.3141046020847</v>
+        <v>132.7497154029261</v>
       </c>
       <c r="E70">
-        <v>64</v>
+        <v>65.125</v>
       </c>
       <c r="F70">
-        <v>76.5</v>
+        <v>77.625</v>
       </c>
       <c r="G70">
         <v>6.97</v>
@@ -7027,28 +7027,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M70">
-        <v>4.15395</v>
+        <v>4.2150375</v>
       </c>
       <c r="N70">
-        <v>23.78482551020408</v>
+        <v>23.72373801020408</v>
       </c>
       <c r="O70">
-        <v>5.94620637755102</v>
+        <v>5.93093450255102</v>
       </c>
       <c r="P70">
-        <v>17.83861913265306</v>
+        <v>17.79280350765306</v>
       </c>
       <c r="Q70">
-        <v>21.83861913265306</v>
+        <v>21.79280350765306</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.384787557572521</v>
+        <v>0.3946686562192133</v>
       </c>
       <c r="T70">
-        <v>2.073205703341882</v>
+        <v>2.13363727261924</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>6.72583336588165</v>
+        <v>6.628357519999307</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1504475334279561</v>
+        <v>0.1500700484327054</v>
       </c>
       <c r="C71">
-        <v>62.09471540292606</v>
+        <v>61.4082039553149</v>
       </c>
       <c r="D71">
-        <v>132.7497154029261</v>
+        <v>133.1882039553149</v>
       </c>
       <c r="E71">
-        <v>65.125</v>
+        <v>66.25000000000001</v>
       </c>
       <c r="F71">
-        <v>77.625</v>
+        <v>78.75000000000001</v>
       </c>
       <c r="G71">
         <v>6.97</v>
@@ -7109,28 +7109,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M71">
-        <v>4.2150375</v>
+        <v>4.276125000000001</v>
       </c>
       <c r="N71">
-        <v>23.72373801020408</v>
+        <v>23.66265051020408</v>
       </c>
       <c r="O71">
-        <v>5.93093450255102</v>
+        <v>5.91566262755102</v>
       </c>
       <c r="P71">
-        <v>17.79280350765306</v>
+        <v>17.74698788265306</v>
       </c>
       <c r="Q71">
-        <v>21.79280350765306</v>
+        <v>21.74698788265306</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3946686562192133</v>
+        <v>0.4052084947756849</v>
       </c>
       <c r="T71">
-        <v>2.13363727261924</v>
+        <v>2.198097613181754</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>6.628357519999307</v>
+        <v>6.53366669828503</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1500700484327054</v>
+        <v>0.1496925634374549</v>
       </c>
       <c r="C72">
-        <v>61.4082039553149</v>
+        <v>60.72459887045393</v>
       </c>
       <c r="D72">
-        <v>133.1882039553149</v>
+        <v>133.6295988704539</v>
       </c>
       <c r="E72">
-        <v>66.25000000000001</v>
+        <v>67.37500000000001</v>
       </c>
       <c r="F72">
-        <v>78.75000000000001</v>
+        <v>79.87500000000001</v>
       </c>
       <c r="G72">
         <v>6.97</v>
@@ -7191,28 +7191,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M72">
-        <v>4.276125000000001</v>
+        <v>4.337212500000001</v>
       </c>
       <c r="N72">
-        <v>23.66265051020408</v>
+        <v>23.60156301020408</v>
       </c>
       <c r="O72">
-        <v>5.91566262755102</v>
+        <v>5.90039075255102</v>
       </c>
       <c r="P72">
-        <v>17.74698788265306</v>
+        <v>17.70117225765306</v>
       </c>
       <c r="Q72">
-        <v>21.74698788265306</v>
+        <v>21.70117225765306</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4052084947756849</v>
+        <v>0.4164752187498444</v>
       </c>
       <c r="T72">
-        <v>2.198097613181754</v>
+        <v>2.267003494472719</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>6.53366669828503</v>
+        <v>6.441643223661298</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1496925634374549</v>
+        <v>0.1493150784422042</v>
       </c>
       <c r="C73">
-        <v>60.72459887045395</v>
+        <v>60.043929140085</v>
       </c>
       <c r="D73">
-        <v>133.6295988704539</v>
+        <v>134.073929140085</v>
       </c>
       <c r="E73">
-        <v>67.375</v>
+        <v>68.5</v>
       </c>
       <c r="F73">
-        <v>79.875</v>
+        <v>81</v>
       </c>
       <c r="G73">
         <v>6.97</v>
@@ -7273,28 +7273,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M73">
-        <v>4.3372125</v>
+        <v>4.3983</v>
       </c>
       <c r="N73">
-        <v>23.60156301020408</v>
+        <v>23.54047551020408</v>
       </c>
       <c r="O73">
-        <v>5.90039075255102</v>
+        <v>5.885118877551021</v>
       </c>
       <c r="P73">
-        <v>17.70117225765306</v>
+        <v>17.65535663265306</v>
       </c>
       <c r="Q73">
-        <v>21.70117225765306</v>
+        <v>21.65535663265306</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4164752187498443</v>
+        <v>0.4285467087221579</v>
       </c>
       <c r="T73">
-        <v>2.267003494472718</v>
+        <v>2.340831224427323</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>6.441643223661299</v>
+        <v>6.352175956666003</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1493150784422042</v>
+        <v>0.1489375934469536</v>
       </c>
       <c r="C74">
-        <v>60.043929140085</v>
+        <v>59.3662241428369</v>
       </c>
       <c r="D74">
-        <v>134.073929140085</v>
+        <v>134.5212241428369</v>
       </c>
       <c r="E74">
-        <v>68.5</v>
+        <v>69.625</v>
       </c>
       <c r="F74">
-        <v>81</v>
+        <v>82.125</v>
       </c>
       <c r="G74">
         <v>6.97</v>
@@ -7355,28 +7355,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M74">
-        <v>4.3983</v>
+        <v>4.4593875</v>
       </c>
       <c r="N74">
-        <v>23.54047551020408</v>
+        <v>23.47938801020408</v>
       </c>
       <c r="O74">
-        <v>5.885118877551021</v>
+        <v>5.869847002551021</v>
       </c>
       <c r="P74">
-        <v>17.65535663265306</v>
+        <v>17.60954100765306</v>
       </c>
       <c r="Q74">
-        <v>21.65535663265306</v>
+        <v>21.60954100765306</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4285467087221579</v>
+        <v>0.4415123831368651</v>
       </c>
       <c r="T74">
-        <v>2.340831224427323</v>
+        <v>2.420127675119305</v>
       </c>
       <c r="U74">
         <v>0.0543</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>6.352175956666003</v>
+        <v>6.265159847670579</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1489375934469536</v>
+        <v>0.148560108451703</v>
       </c>
       <c r="C75">
-        <v>59.3662241428369</v>
+        <v>58.69151365070039</v>
       </c>
       <c r="D75">
-        <v>134.5212241428369</v>
+        <v>134.9715136507004</v>
       </c>
       <c r="E75">
-        <v>69.625</v>
+        <v>70.75</v>
       </c>
       <c r="F75">
-        <v>82.125</v>
+        <v>83.25</v>
       </c>
       <c r="G75">
         <v>6.97</v>
@@ -7437,28 +7437,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M75">
-        <v>4.4593875</v>
+        <v>4.520475</v>
       </c>
       <c r="N75">
-        <v>23.47938801020408</v>
+        <v>23.41830051020408</v>
       </c>
       <c r="O75">
-        <v>5.869847002551021</v>
+        <v>5.85457512755102</v>
       </c>
       <c r="P75">
-        <v>17.60954100765306</v>
+        <v>17.56372538265306</v>
       </c>
       <c r="Q75">
-        <v>21.60954100765306</v>
+        <v>21.56372538265306</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4415123831368651</v>
+        <v>0.4554754171219345</v>
       </c>
       <c r="T75">
-        <v>2.420127675119305</v>
+        <v>2.505523852787594</v>
       </c>
       <c r="U75">
         <v>0.0543</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>6.265159847670579</v>
+        <v>6.180495525404759</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.148560108451703</v>
+        <v>0.1487451234564524</v>
       </c>
       <c r="C76">
-        <v>58.69151365070039</v>
+        <v>57.34543924601999</v>
       </c>
       <c r="D76">
-        <v>134.9715136507004</v>
+        <v>134.75043924602</v>
       </c>
       <c r="E76">
-        <v>70.75</v>
+        <v>71.875</v>
       </c>
       <c r="F76">
-        <v>83.25</v>
+        <v>84.375</v>
       </c>
       <c r="G76">
         <v>6.97</v>
@@ -7519,45 +7519,45 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M76">
-        <v>4.520475</v>
+        <v>4.6659375</v>
       </c>
       <c r="N76">
-        <v>23.41830051020408</v>
+        <v>23.27283801020408</v>
       </c>
       <c r="O76">
-        <v>5.85457512755102</v>
+        <v>5.818209502551021</v>
       </c>
       <c r="P76">
-        <v>17.56372538265306</v>
+        <v>17.45462850765306</v>
       </c>
       <c r="Q76">
-        <v>21.56372538265306</v>
+        <v>21.45462850765306</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4554754171219345</v>
+        <v>0.4705554938258094</v>
       </c>
       <c r="T76">
-        <v>2.505523852787594</v>
+        <v>2.597751724669346</v>
       </c>
       <c r="U76">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V76">
         <v>0.25</v>
       </c>
       <c r="W76">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y76">
-        <v>6.180495525404759</v>
+        <v>5.987816062732105</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1487451234564524</v>
+        <v>0.1483751384612017</v>
       </c>
       <c r="C77">
-        <v>57.34543924601999</v>
+        <v>56.66326059311874</v>
       </c>
       <c r="D77">
-        <v>134.75043924602</v>
+        <v>135.1932605931187</v>
       </c>
       <c r="E77">
-        <v>71.875</v>
+        <v>73</v>
       </c>
       <c r="F77">
-        <v>84.375</v>
+        <v>85.5</v>
       </c>
       <c r="G77">
         <v>6.97</v>
@@ -7601,28 +7601,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M77">
-        <v>4.6659375</v>
+        <v>4.72815</v>
       </c>
       <c r="N77">
-        <v>23.27283801020408</v>
+        <v>23.21062551020408</v>
       </c>
       <c r="O77">
-        <v>5.818209502551021</v>
+        <v>5.80265637755102</v>
       </c>
       <c r="P77">
-        <v>17.45462850765306</v>
+        <v>17.40796913265306</v>
       </c>
       <c r="Q77">
-        <v>21.45462850765306</v>
+        <v>21.40796913265306</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4705554938258094</v>
+        <v>0.4868922435883405</v>
       </c>
       <c r="T77">
-        <v>2.597751724669346</v>
+        <v>2.697665252541244</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.987816062732105</v>
+        <v>5.909029009275104</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1483751384612017</v>
+        <v>0.1480051534659511</v>
       </c>
       <c r="C78">
-        <v>56.66326059311874</v>
+        <v>55.98400196439056</v>
       </c>
       <c r="D78">
-        <v>135.1932605931187</v>
+        <v>135.6390019643906</v>
       </c>
       <c r="E78">
-        <v>73</v>
+        <v>74.125</v>
       </c>
       <c r="F78">
-        <v>85.5</v>
+        <v>86.625</v>
       </c>
       <c r="G78">
         <v>6.97</v>
@@ -7683,28 +7683,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M78">
-        <v>4.72815</v>
+        <v>4.790362500000001</v>
       </c>
       <c r="N78">
-        <v>23.21062551020408</v>
+        <v>23.14841301020408</v>
       </c>
       <c r="O78">
-        <v>5.80265637755102</v>
+        <v>5.78710325255102</v>
       </c>
       <c r="P78">
-        <v>17.40796913265306</v>
+        <v>17.36130975765306</v>
       </c>
       <c r="Q78">
-        <v>21.40796913265306</v>
+        <v>21.36130975765306</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4868922435883405</v>
+        <v>0.5046495802867439</v>
       </c>
       <c r="T78">
-        <v>2.697665252541244</v>
+        <v>2.806266913271568</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.909029009275104</v>
+        <v>5.832288372791011</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1480051534659511</v>
+        <v>0.1476351684707005</v>
       </c>
       <c r="C79">
-        <v>55.98400196439056</v>
+        <v>55.30769233793282</v>
       </c>
       <c r="D79">
-        <v>135.6390019643906</v>
+        <v>136.0876923379328</v>
       </c>
       <c r="E79">
-        <v>74.125</v>
+        <v>75.25</v>
       </c>
       <c r="F79">
-        <v>86.625</v>
+        <v>87.75</v>
       </c>
       <c r="G79">
         <v>6.97</v>
@@ -7765,28 +7765,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M79">
-        <v>4.790362500000001</v>
+        <v>4.852575</v>
       </c>
       <c r="N79">
-        <v>23.14841301020408</v>
+        <v>23.08620051020408</v>
       </c>
       <c r="O79">
-        <v>5.78710325255102</v>
+        <v>5.77155012755102</v>
       </c>
       <c r="P79">
-        <v>17.36130975765306</v>
+        <v>17.31465038265306</v>
       </c>
       <c r="Q79">
-        <v>21.36130975765306</v>
+        <v>21.31465038265306</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5046495802867439</v>
+        <v>0.5240212203213658</v>
       </c>
       <c r="T79">
-        <v>2.806266913271568</v>
+        <v>2.924741452250103</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.832288372791011</v>
+        <v>5.757515444934716</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1476351684707005</v>
+        <v>0.1472651834754498</v>
       </c>
       <c r="C80">
-        <v>55.30769233793282</v>
+        <v>54.63436107655079</v>
       </c>
       <c r="D80">
-        <v>136.0876923379328</v>
+        <v>136.5393610765508</v>
       </c>
       <c r="E80">
-        <v>75.25</v>
+        <v>76.375</v>
       </c>
       <c r="F80">
-        <v>87.75</v>
+        <v>88.875</v>
       </c>
       <c r="G80">
         <v>6.97</v>
@@ -7847,28 +7847,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M80">
-        <v>4.852575</v>
+        <v>4.9147875</v>
       </c>
       <c r="N80">
-        <v>23.08620051020408</v>
+        <v>23.02398801020408</v>
       </c>
       <c r="O80">
-        <v>5.77155012755102</v>
+        <v>5.755997002551021</v>
       </c>
       <c r="P80">
-        <v>17.31465038265306</v>
+        <v>17.26799100765306</v>
       </c>
       <c r="Q80">
-        <v>21.31465038265306</v>
+        <v>21.26799100765306</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5240212203213658</v>
+        <v>0.5452377784545231</v>
       </c>
       <c r="T80">
-        <v>2.924741452250103</v>
+        <v>3.054499280655165</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.757515444934716</v>
+        <v>5.68463550259377</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1472651834754498</v>
+        <v>0.1468951984801992</v>
       </c>
       <c r="C81">
-        <v>54.63436107655079</v>
+        <v>53.96403793416297</v>
       </c>
       <c r="D81">
-        <v>136.5393610765508</v>
+        <v>136.994037934163</v>
       </c>
       <c r="E81">
-        <v>76.375</v>
+        <v>77.5</v>
       </c>
       <c r="F81">
-        <v>88.875</v>
+        <v>90</v>
       </c>
       <c r="G81">
         <v>6.97</v>
@@ -7929,28 +7929,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M81">
-        <v>4.9147875</v>
+        <v>4.977</v>
       </c>
       <c r="N81">
-        <v>23.02398801020408</v>
+        <v>22.96177551020408</v>
       </c>
       <c r="O81">
-        <v>5.755997002551021</v>
+        <v>5.74044387755102</v>
       </c>
       <c r="P81">
-        <v>17.26799100765306</v>
+        <v>17.22133163265306</v>
       </c>
       <c r="Q81">
-        <v>21.26799100765306</v>
+        <v>21.22133163265306</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5452377784545231</v>
+        <v>0.5685759924009963</v>
       </c>
       <c r="T81">
-        <v>3.054499280655165</v>
+        <v>3.197232891900734</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.68463550259377</v>
+        <v>5.613577558811348</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1468951984801992</v>
+        <v>0.1465252134849486</v>
       </c>
       <c r="C82">
-        <v>53.96403793416297</v>
+        <v>53.296753062335</v>
       </c>
       <c r="D82">
-        <v>136.994037934163</v>
+        <v>137.451753062335</v>
       </c>
       <c r="E82">
-        <v>77.5</v>
+        <v>78.625</v>
       </c>
       <c r="F82">
-        <v>90</v>
+        <v>91.125</v>
       </c>
       <c r="G82">
         <v>6.97</v>
@@ -8011,28 +8011,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M82">
-        <v>4.977</v>
+        <v>5.039212500000001</v>
       </c>
       <c r="N82">
-        <v>22.96177551020408</v>
+        <v>22.89956301020408</v>
       </c>
       <c r="O82">
-        <v>5.74044387755102</v>
+        <v>5.72489075255102</v>
       </c>
       <c r="P82">
-        <v>17.22133163265306</v>
+        <v>17.17467225765306</v>
       </c>
       <c r="Q82">
-        <v>21.22133163265306</v>
+        <v>21.17467225765306</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5685759924009963</v>
+        <v>0.5943708604470981</v>
       </c>
       <c r="T82">
-        <v>3.197232891900734</v>
+        <v>3.354991093803731</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.613577558811348</v>
+        <v>5.544274132159356</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1465252134849486</v>
+        <v>0.146155228489698</v>
       </c>
       <c r="C83">
-        <v>53.296753062335</v>
+        <v>52.63253701694453</v>
       </c>
       <c r="D83">
-        <v>137.451753062335</v>
+        <v>137.9125370169445</v>
       </c>
       <c r="E83">
-        <v>78.625</v>
+        <v>79.75</v>
       </c>
       <c r="F83">
-        <v>91.125</v>
+        <v>92.25</v>
       </c>
       <c r="G83">
         <v>6.97</v>
@@ -8093,28 +8093,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M83">
-        <v>5.039212500000001</v>
+        <v>5.101425</v>
       </c>
       <c r="N83">
-        <v>22.89956301020408</v>
+        <v>22.83735051020408</v>
       </c>
       <c r="O83">
-        <v>5.72489075255102</v>
+        <v>5.709337627551021</v>
       </c>
       <c r="P83">
-        <v>17.17467225765306</v>
+        <v>17.12801288265306</v>
       </c>
       <c r="Q83">
-        <v>21.17467225765306</v>
+        <v>21.12801288265306</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5943708604470981</v>
+        <v>0.6230318249427668</v>
       </c>
       <c r="T83">
-        <v>3.354991093803731</v>
+        <v>3.530277984807061</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.544274132159356</v>
+        <v>5.476661032986682</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.146155228489698</v>
+        <v>0.1457852434944474</v>
       </c>
       <c r="C84">
-        <v>52.63253701694453</v>
+        <v>51.9714207649814</v>
       </c>
       <c r="D84">
-        <v>137.9125370169445</v>
+        <v>138.3764207649814</v>
       </c>
       <c r="E84">
-        <v>79.75</v>
+        <v>80.87500000000001</v>
       </c>
       <c r="F84">
-        <v>92.25</v>
+        <v>93.37500000000001</v>
       </c>
       <c r="G84">
         <v>6.97</v>
@@ -8175,28 +8175,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M84">
-        <v>5.101425</v>
+        <v>5.163637500000001</v>
       </c>
       <c r="N84">
-        <v>22.83735051020408</v>
+        <v>22.77513801020408</v>
       </c>
       <c r="O84">
-        <v>5.709337627551021</v>
+        <v>5.69378450255102</v>
       </c>
       <c r="P84">
-        <v>17.12801288265306</v>
+        <v>17.08135350765306</v>
       </c>
       <c r="Q84">
-        <v>21.12801288265306</v>
+        <v>21.08135350765306</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6230318249427668</v>
+        <v>0.6550646676143965</v>
       </c>
       <c r="T84">
-        <v>3.530277984807061</v>
+        <v>3.726186862987253</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.476661032986682</v>
+        <v>5.410677165119371</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1457852434944474</v>
+        <v>0.1454152584991967</v>
       </c>
       <c r="C85">
-        <v>51.9714207649814</v>
+        <v>51.31343569148503</v>
       </c>
       <c r="D85">
-        <v>138.3764207649814</v>
+        <v>138.843435691485</v>
       </c>
       <c r="E85">
-        <v>80.87500000000001</v>
+        <v>82.00000000000001</v>
       </c>
       <c r="F85">
-        <v>93.37500000000001</v>
+        <v>94.50000000000001</v>
       </c>
       <c r="G85">
         <v>6.97</v>
@@ -8257,28 +8257,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M85">
-        <v>5.163637500000001</v>
+        <v>5.225850000000001</v>
       </c>
       <c r="N85">
-        <v>22.77513801020408</v>
+        <v>22.71292551020408</v>
       </c>
       <c r="O85">
-        <v>5.69378450255102</v>
+        <v>5.67823137755102</v>
       </c>
       <c r="P85">
-        <v>17.08135350765306</v>
+        <v>17.03469413265306</v>
       </c>
       <c r="Q85">
-        <v>21.08135350765306</v>
+        <v>21.03469413265306</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6550646676143965</v>
+        <v>0.69110161561998</v>
       </c>
       <c r="T85">
-        <v>3.726186862987253</v>
+        <v>3.94658435093997</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.410677165119371</v>
+        <v>5.346264341725092</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1454152584991967</v>
+        <v>0.1450452735039461</v>
       </c>
       <c r="C86">
-        <v>51.31343569148504</v>
+        <v>50.65861360662234</v>
       </c>
       <c r="D86">
-        <v>138.843435691485</v>
+        <v>139.3136136066223</v>
       </c>
       <c r="E86">
-        <v>82</v>
+        <v>83.125</v>
       </c>
       <c r="F86">
-        <v>94.5</v>
+        <v>95.625</v>
       </c>
       <c r="G86">
         <v>6.97</v>
@@ -8339,28 +8339,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M86">
-        <v>5.22585</v>
+        <v>5.288062500000001</v>
       </c>
       <c r="N86">
-        <v>22.71292551020408</v>
+        <v>22.65071301020408</v>
       </c>
       <c r="O86">
-        <v>5.67823137755102</v>
+        <v>5.66267825255102</v>
       </c>
       <c r="P86">
-        <v>17.03469413265306</v>
+        <v>16.98803475765306</v>
       </c>
       <c r="Q86">
-        <v>21.03469413265306</v>
+        <v>20.98803475765306</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6911016156199795</v>
+        <v>0.7319434900263074</v>
       </c>
       <c r="T86">
-        <v>3.946584350939967</v>
+        <v>4.196368170619713</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.346264341725093</v>
+        <v>5.283367114175386</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1450452735039461</v>
+        <v>0.1446752885086955</v>
       </c>
       <c r="C87">
-        <v>50.65861360662234</v>
+        <v>50.00698675291108</v>
       </c>
       <c r="D87">
-        <v>139.3136136066223</v>
+        <v>139.7869867529111</v>
       </c>
       <c r="E87">
-        <v>83.125</v>
+        <v>84.25</v>
       </c>
       <c r="F87">
-        <v>95.625</v>
+        <v>96.75</v>
       </c>
       <c r="G87">
         <v>6.97</v>
@@ -8421,28 +8421,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M87">
-        <v>5.288062500000001</v>
+        <v>5.350275</v>
       </c>
       <c r="N87">
-        <v>22.65071301020408</v>
+        <v>22.58850051020408</v>
       </c>
       <c r="O87">
-        <v>5.66267825255102</v>
+        <v>5.64712512755102</v>
       </c>
       <c r="P87">
-        <v>16.98803475765306</v>
+        <v>16.94137538265306</v>
       </c>
       <c r="Q87">
-        <v>20.98803475765306</v>
+        <v>20.94137538265306</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7319434900263074</v>
+        <v>0.7786199179192534</v>
       </c>
       <c r="T87">
-        <v>4.196368170619713</v>
+        <v>4.481835393110849</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.283367114175386</v>
+        <v>5.221932612847766</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1446752885086955</v>
+        <v>0.1443053035134448</v>
       </c>
       <c r="C88">
-        <v>50.00698675291108</v>
+        <v>49.35858781258983</v>
       </c>
       <c r="D88">
-        <v>139.7869867529111</v>
+        <v>140.2635878125898</v>
       </c>
       <c r="E88">
-        <v>84.25</v>
+        <v>85.375</v>
       </c>
       <c r="F88">
-        <v>96.75</v>
+        <v>97.875</v>
       </c>
       <c r="G88">
         <v>6.97</v>
@@ -8503,28 +8503,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M88">
-        <v>5.350275</v>
+        <v>5.4124875</v>
       </c>
       <c r="N88">
-        <v>22.58850051020408</v>
+        <v>22.52628801020408</v>
       </c>
       <c r="O88">
-        <v>5.64712512755102</v>
+        <v>5.63157200255102</v>
       </c>
       <c r="P88">
-        <v>16.94137538265306</v>
+        <v>16.89471600765306</v>
       </c>
       <c r="Q88">
-        <v>20.94137538265306</v>
+        <v>20.89471600765306</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7786199179192534</v>
+        <v>0.8324773347188066</v>
       </c>
       <c r="T88">
-        <v>4.481835393110849</v>
+        <v>4.811220649831391</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.221932612847766</v>
+        <v>5.161910398906987</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1443053035134448</v>
+        <v>0.1439353185181942</v>
       </c>
       <c r="C89">
-        <v>49.35858781258983</v>
+        <v>48.71344991513988</v>
       </c>
       <c r="D89">
-        <v>140.2635878125898</v>
+        <v>140.7434499151399</v>
       </c>
       <c r="E89">
-        <v>85.375</v>
+        <v>86.5</v>
       </c>
       <c r="F89">
-        <v>97.875</v>
+        <v>99</v>
       </c>
       <c r="G89">
         <v>6.97</v>
@@ -8585,28 +8585,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M89">
-        <v>5.4124875</v>
+        <v>5.4747</v>
       </c>
       <c r="N89">
-        <v>22.52628801020408</v>
+        <v>22.46407551020408</v>
       </c>
       <c r="O89">
-        <v>5.63157200255102</v>
+        <v>5.616018877551021</v>
       </c>
       <c r="P89">
-        <v>16.89471600765306</v>
+        <v>16.84805663265306</v>
       </c>
       <c r="Q89">
-        <v>20.89471600765306</v>
+        <v>20.84805663265306</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8324773347188066</v>
+        <v>0.8953109876516188</v>
       </c>
       <c r="T89">
-        <v>4.811220649831391</v>
+        <v>5.195503449338692</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.161910398906987</v>
+        <v>5.103252326192135</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1439353185181942</v>
+        <v>0.1435653335229436</v>
       </c>
       <c r="C90">
-        <v>48.71344991513988</v>
+        <v>48.07160664496212</v>
       </c>
       <c r="D90">
-        <v>140.7434499151399</v>
+        <v>141.2266066449621</v>
       </c>
       <c r="E90">
-        <v>86.5</v>
+        <v>87.625</v>
       </c>
       <c r="F90">
-        <v>99</v>
+        <v>100.125</v>
       </c>
       <c r="G90">
         <v>6.97</v>
@@ -8667,28 +8667,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M90">
-        <v>5.4747</v>
+        <v>5.536912500000001</v>
       </c>
       <c r="N90">
-        <v>22.46407551020408</v>
+        <v>22.40186301020408</v>
       </c>
       <c r="O90">
-        <v>5.616018877551021</v>
+        <v>5.60046575255102</v>
       </c>
       <c r="P90">
-        <v>16.84805663265306</v>
+        <v>16.80139725765306</v>
       </c>
       <c r="Q90">
-        <v>20.84805663265306</v>
+        <v>20.80139725765306</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8953109876516188</v>
+        <v>0.9695689411176693</v>
       </c>
       <c r="T90">
-        <v>5.195503449338692</v>
+        <v>5.649655848756409</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.103252326192135</v>
+        <v>5.045912412414695</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1435653335229436</v>
+        <v>0.143195348527693</v>
       </c>
       <c r="C91">
-        <v>48.07160664496212</v>
+        <v>47.43309204921206</v>
       </c>
       <c r="D91">
-        <v>141.2266066449621</v>
+        <v>141.7130920492121</v>
       </c>
       <c r="E91">
-        <v>87.625</v>
+        <v>88.75</v>
       </c>
       <c r="F91">
-        <v>100.125</v>
+        <v>101.25</v>
       </c>
       <c r="G91">
         <v>6.97</v>
@@ -8749,28 +8749,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M91">
-        <v>5.536912500000001</v>
+        <v>5.599125</v>
       </c>
       <c r="N91">
-        <v>22.40186301020408</v>
+        <v>22.33965051020408</v>
       </c>
       <c r="O91">
-        <v>5.60046575255102</v>
+        <v>5.58491262755102</v>
       </c>
       <c r="P91">
-        <v>16.80139725765306</v>
+        <v>16.75473788265306</v>
       </c>
       <c r="Q91">
-        <v>20.80139725765306</v>
+        <v>20.75473788265306</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9695689411176693</v>
+        <v>1.05867848527693</v>
       </c>
       <c r="T91">
-        <v>5.649655848756409</v>
+        <v>6.194638728057672</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.045912412414695</v>
+        <v>4.98984671894342</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.143195348527693</v>
+        <v>0.1428253635324424</v>
       </c>
       <c r="C92">
-        <v>47.43309204921206</v>
+        <v>46.79794064579781</v>
       </c>
       <c r="D92">
-        <v>141.7130920492121</v>
+        <v>142.2029406457978</v>
       </c>
       <c r="E92">
-        <v>88.75</v>
+        <v>89.875</v>
       </c>
       <c r="F92">
-        <v>101.25</v>
+        <v>102.375</v>
       </c>
       <c r="G92">
         <v>6.97</v>
@@ -8831,28 +8831,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M92">
-        <v>5.599125</v>
+        <v>5.6613375</v>
       </c>
       <c r="N92">
-        <v>22.33965051020408</v>
+        <v>22.27743801020408</v>
       </c>
       <c r="O92">
-        <v>5.58491262755102</v>
+        <v>5.56935950255102</v>
       </c>
       <c r="P92">
-        <v>16.75473788265306</v>
+        <v>16.70807850765306</v>
       </c>
       <c r="Q92">
-        <v>20.75473788265306</v>
+        <v>20.70807850765306</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.05867848527693</v>
+        <v>1.167590150360471</v>
       </c>
       <c r="T92">
-        <v>6.194638728057672</v>
+        <v>6.860728913870325</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.98984671894342</v>
+        <v>4.93501323851547</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1428253635324424</v>
+        <v>0.1424553785371918</v>
       </c>
       <c r="C93">
-        <v>46.79794064579781</v>
+        <v>46.1661874315443</v>
       </c>
       <c r="D93">
-        <v>142.2029406457978</v>
+        <v>142.6961874315443</v>
       </c>
       <c r="E93">
-        <v>89.875</v>
+        <v>91</v>
       </c>
       <c r="F93">
-        <v>102.375</v>
+        <v>103.5</v>
       </c>
       <c r="G93">
         <v>6.97</v>
@@ -8913,28 +8913,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M93">
-        <v>5.6613375</v>
+        <v>5.72355</v>
       </c>
       <c r="N93">
-        <v>22.27743801020408</v>
+        <v>22.21522551020408</v>
       </c>
       <c r="O93">
-        <v>5.56935950255102</v>
+        <v>5.55380637755102</v>
       </c>
       <c r="P93">
-        <v>16.70807850765306</v>
+        <v>16.66141913265306</v>
       </c>
       <c r="Q93">
-        <v>20.70807850765306</v>
+        <v>20.66141913265306</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.167590150360471</v>
+        <v>1.303729731714898</v>
       </c>
       <c r="T93">
-        <v>6.860728913870325</v>
+        <v>7.693341646136144</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.93501323851547</v>
+        <v>4.881371790270737</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1424553785371918</v>
+        <v>0.1420853935419412</v>
       </c>
       <c r="C94">
-        <v>46.1661874315443</v>
+        <v>45.53786789052833</v>
       </c>
       <c r="D94">
-        <v>142.6961874315443</v>
+        <v>143.1928678905283</v>
       </c>
       <c r="E94">
-        <v>91</v>
+        <v>92.125</v>
       </c>
       <c r="F94">
-        <v>103.5</v>
+        <v>104.625</v>
       </c>
       <c r="G94">
         <v>6.97</v>
@@ -8995,28 +8995,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M94">
-        <v>5.72355</v>
+        <v>5.785762500000001</v>
       </c>
       <c r="N94">
-        <v>22.21522551020408</v>
+        <v>22.15301301020408</v>
       </c>
       <c r="O94">
-        <v>5.55380637755102</v>
+        <v>5.53825325255102</v>
       </c>
       <c r="P94">
-        <v>16.66141913265306</v>
+        <v>16.61475975765306</v>
       </c>
       <c r="Q94">
-        <v>20.66141913265306</v>
+        <v>20.61475975765306</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.303729731714898</v>
+        <v>1.478766336313446</v>
       </c>
       <c r="T94">
-        <v>7.693341646136144</v>
+        <v>8.763843730477909</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.881371790270737</v>
+        <v>4.828883921558148</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1420853935419412</v>
+        <v>0.1417154085466905</v>
       </c>
       <c r="C95">
-        <v>45.53786789052833</v>
+        <v>44.91301800258768</v>
       </c>
       <c r="D95">
-        <v>143.1928678905283</v>
+        <v>143.6930180025877</v>
       </c>
       <c r="E95">
-        <v>92.125</v>
+        <v>93.25</v>
       </c>
       <c r="F95">
-        <v>104.625</v>
+        <v>105.75</v>
       </c>
       <c r="G95">
         <v>6.97</v>
@@ -9077,28 +9077,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M95">
-        <v>5.785762500000001</v>
+        <v>5.847975</v>
       </c>
       <c r="N95">
-        <v>22.15301301020408</v>
+        <v>22.09080051020408</v>
       </c>
       <c r="O95">
-        <v>5.53825325255102</v>
+        <v>5.522700127551021</v>
       </c>
       <c r="P95">
-        <v>16.61475975765306</v>
+        <v>16.56810038265306</v>
       </c>
       <c r="Q95">
-        <v>20.61475975765306</v>
+        <v>20.56810038265306</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.478766336313446</v>
+        <v>1.712148475778177</v>
       </c>
       <c r="T95">
-        <v>8.763843730477909</v>
+        <v>10.1911798429336</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.828883921558148</v>
+        <v>4.777512816009659</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1417154085466905</v>
+        <v>0.1413454235514399</v>
       </c>
       <c r="C96">
-        <v>44.91301800258768</v>
+        <v>44.29167425200966</v>
       </c>
       <c r="D96">
-        <v>143.6930180025877</v>
+        <v>144.1966742520097</v>
       </c>
       <c r="E96">
-        <v>93.25</v>
+        <v>94.37500000000001</v>
       </c>
       <c r="F96">
-        <v>105.75</v>
+        <v>106.875</v>
       </c>
       <c r="G96">
         <v>6.97</v>
@@ -9159,28 +9159,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M96">
-        <v>5.847975</v>
+        <v>5.910187500000001</v>
       </c>
       <c r="N96">
-        <v>22.09080051020408</v>
+        <v>22.02858801020408</v>
       </c>
       <c r="O96">
-        <v>5.522700127551021</v>
+        <v>5.507147002551021</v>
       </c>
       <c r="P96">
-        <v>16.56810038265306</v>
+        <v>16.52144100765306</v>
       </c>
       <c r="Q96">
-        <v>20.56810038265306</v>
+        <v>20.52144100765306</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.712148475778177</v>
+        <v>2.038883471028801</v>
       </c>
       <c r="T96">
-        <v>10.1911798429336</v>
+        <v>12.18945040037156</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.777512816009659</v>
+        <v>4.727223207420082</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1413454235514399</v>
+        <v>0.1409754385561893</v>
       </c>
       <c r="C97">
-        <v>44.29167425200966</v>
+        <v>43.67387363640309</v>
       </c>
       <c r="D97">
-        <v>144.1966742520097</v>
+        <v>144.7038736364031</v>
       </c>
       <c r="E97">
-        <v>94.37500000000001</v>
+        <v>95.50000000000001</v>
       </c>
       <c r="F97">
-        <v>106.875</v>
+        <v>108</v>
       </c>
       <c r="G97">
         <v>6.97</v>
@@ -9241,28 +9241,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M97">
-        <v>5.910187500000001</v>
+        <v>5.972400000000001</v>
       </c>
       <c r="N97">
-        <v>22.02858801020408</v>
+        <v>21.96637551020408</v>
       </c>
       <c r="O97">
-        <v>5.507147002551021</v>
+        <v>5.49159387755102</v>
       </c>
       <c r="P97">
-        <v>16.52144100765306</v>
+        <v>16.47478163265306</v>
       </c>
       <c r="Q97">
-        <v>20.52144100765306</v>
+        <v>20.47478163265306</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.038883471028801</v>
+        <v>2.528985963904736</v>
       </c>
       <c r="T97">
-        <v>12.18945040037156</v>
+        <v>15.18685623652851</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.727223207420082</v>
+        <v>4.677981299009456</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1409754385561893</v>
+        <v>0.1406054535609386</v>
       </c>
       <c r="C98">
-        <v>43.6738736364031</v>
+        <v>43.05965367575774</v>
       </c>
       <c r="D98">
-        <v>144.7038736364031</v>
+        <v>145.2146536757577</v>
       </c>
       <c r="E98">
-        <v>95.5</v>
+        <v>96.625</v>
       </c>
       <c r="F98">
-        <v>108</v>
+        <v>109.125</v>
       </c>
       <c r="G98">
         <v>6.97</v>
@@ -9323,28 +9323,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M98">
-        <v>5.9724</v>
+        <v>6.034612500000001</v>
       </c>
       <c r="N98">
-        <v>21.96637551020408</v>
+        <v>21.90416301020408</v>
       </c>
       <c r="O98">
-        <v>5.49159387755102</v>
+        <v>5.47604075255102</v>
       </c>
       <c r="P98">
-        <v>16.47478163265306</v>
+        <v>16.42812225765306</v>
       </c>
       <c r="Q98">
-        <v>20.47478163265306</v>
+        <v>20.42812225765306</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.52898596390473</v>
+        <v>3.345823452031286</v>
       </c>
       <c r="T98">
-        <v>15.18685623652847</v>
+        <v>20.18253263012336</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.677981299009456</v>
+        <v>4.629754687679462</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1406054535609386</v>
+        <v>0.140235468565688</v>
       </c>
       <c r="C99">
-        <v>43.05965367575774</v>
+        <v>42.44905242169662</v>
       </c>
       <c r="D99">
-        <v>145.2146536757577</v>
+        <v>145.7290524216966</v>
       </c>
       <c r="E99">
-        <v>96.625</v>
+        <v>97.75</v>
       </c>
       <c r="F99">
-        <v>109.125</v>
+        <v>110.25</v>
       </c>
       <c r="G99">
         <v>6.97</v>
@@ -9405,28 +9405,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M99">
-        <v>6.034612500000001</v>
+        <v>6.096825</v>
       </c>
       <c r="N99">
-        <v>21.90416301020408</v>
+        <v>21.84195051020408</v>
       </c>
       <c r="O99">
-        <v>5.47604075255102</v>
+        <v>5.460487627551021</v>
       </c>
       <c r="P99">
-        <v>16.42812225765306</v>
+        <v>16.38146288265306</v>
       </c>
       <c r="Q99">
-        <v>20.42812225765306</v>
+        <v>20.38146288265306</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.345823452031286</v>
+        <v>4.979498428284398</v>
       </c>
       <c r="T99">
-        <v>20.18253263012336</v>
+        <v>30.17388541731315</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.629754687679462</v>
+        <v>4.582512292907223</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.140235468565688</v>
+        <v>0.1398654835704374</v>
       </c>
       <c r="C100">
-        <v>42.44905242169662</v>
+        <v>41.84210846692571</v>
       </c>
       <c r="D100">
-        <v>145.7290524216966</v>
+        <v>146.2471084669257</v>
       </c>
       <c r="E100">
-        <v>97.75</v>
+        <v>98.875</v>
       </c>
       <c r="F100">
-        <v>110.25</v>
+        <v>111.375</v>
       </c>
       <c r="G100">
         <v>6.97</v>
@@ -9487,28 +9487,28 @@
         <v>27.93877551020408</v>
       </c>
       <c r="M100">
-        <v>6.096825</v>
+        <v>6.1590375</v>
       </c>
       <c r="N100">
-        <v>21.84195051020408</v>
+        <v>21.77973801020408</v>
       </c>
       <c r="O100">
-        <v>5.460487627551021</v>
+        <v>5.44493450255102</v>
       </c>
       <c r="P100">
-        <v>16.38146288265306</v>
+        <v>16.33480350765306</v>
       </c>
       <c r="Q100">
-        <v>20.38146288265306</v>
+        <v>20.33480350765306</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.979498428284398</v>
+        <v>9.880523357043733</v>
       </c>
       <c r="T100">
-        <v>30.17388541731315</v>
+        <v>60.1479437788825</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.582512292907223</v>
+        <v>4.536224289948564</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1398654835704374</v>
-      </c>
-      <c r="C101">
-        <v>41.84210846692571</v>
-      </c>
-      <c r="D101">
-        <v>146.2471084669257</v>
-      </c>
-      <c r="E101">
-        <v>98.875</v>
-      </c>
-      <c r="F101">
-        <v>111.375</v>
-      </c>
-      <c r="G101">
-        <v>6.97</v>
-      </c>
-      <c r="H101">
-        <v>100</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>31.93877551020408</v>
-      </c>
-      <c r="K101">
-        <v>4</v>
-      </c>
-      <c r="L101">
-        <v>27.93877551020408</v>
-      </c>
-      <c r="M101">
-        <v>6.1590375</v>
-      </c>
-      <c r="N101">
-        <v>21.77973801020408</v>
-      </c>
-      <c r="O101">
-        <v>5.44493450255102</v>
-      </c>
-      <c r="P101">
-        <v>16.33480350765306</v>
-      </c>
-      <c r="Q101">
-        <v>20.33480350765306</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.880523357043733</v>
-      </c>
-      <c r="T101">
-        <v>60.1479437788825</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.041475</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.536224289948564</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
